--- a/raw/trektellen/Trektellen_headerdata_2422_2024.xlsx
+++ b/raw/trektellen/Trektellen_headerdata_2422_2024.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="899">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="902">
   <si>
     <t>id</t>
   </si>
@@ -77,6 +77,12 @@
     <t>temperature</t>
   </si>
   <si>
+    <t>hydro</t>
+  </si>
+  <si>
+    <t>hpa</t>
+  </si>
+  <si>
     <t>observersactive</t>
   </si>
   <si>
@@ -1817,7 +1823,7 @@
     <t>2024-10-07 20:47:39.565436</t>
   </si>
   <si>
-    <t>2024-10-08 07:44:00</t>
+    <t>2024-10-08 13:45:00</t>
   </si>
   <si>
     <t>2024-10-08 19:02:00</t>
@@ -1826,13 +1832,16 @@
     <t>Tiphaine Causse, Maeve Briand</t>
   </si>
   <si>
-    <t>Pas de stratus sur le Rhône. Vent de SSO (5-15km/h). Pluie jusqu'à 14h30. Cumulus et Nimbostratus. Puis se découvre sur la fin de journée. 11-12°C</t>
+    <t>Pas de stratus sur le Rhône. Vent de SSO (5-15km/h). Pluie jusqu&amp;#039;à 14h30. Cumulus et Nimbostratus. Puis se découvre sur la fin de journée. 11-12°C</t>
   </si>
   <si>
     <t>Pas de spot avant 13h45 pour raison de pluie. Quelques hirondelles et busards passeront en fin de journée comme ces 11 hérons en HP. Une courte journée reposante.</t>
   </si>
   <si>
     <t>2024-10-08 20:07:02.598267</t>
+  </si>
+  <si>
+    <t>2026-10-13 09:11:27.605993</t>
   </si>
   <si>
     <t>2024-10-09 07:46:00</t>
@@ -3050,10 +3059,10 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:AB132"/>
+  <dimension ref="A1:AD132"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:28">
+    <row r="1" spans="1:30">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3138,8 +3147,14 @@
       <c r="AB1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="2" spans="1:28">
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30">
       <c r="A2">
         <v>2770382</v>
       </c>
@@ -3162,25 +3177,19 @@
         <v>2024</v>
       </c>
       <c r="H2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="T2">
         <v>0</v>
-      </c>
-      <c r="W2" t="s">
-        <v>32</v>
-      </c>
-      <c r="X2" t="s">
-        <v>33</v>
       </c>
       <c r="Y2" t="s">
         <v>34</v>
@@ -3192,10 +3201,16 @@
         <v>36</v>
       </c>
       <c r="AB2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:30">
       <c r="A3">
         <v>2770683</v>
       </c>
@@ -3218,40 +3233,40 @@
         <v>2024</v>
       </c>
       <c r="H3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="T3">
         <v>0</v>
       </c>
-      <c r="W3" t="s">
-        <v>32</v>
-      </c>
-      <c r="X3" t="s">
-        <v>40</v>
-      </c>
       <c r="Y3" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="Z3" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="AA3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AB3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:30">
       <c r="A4">
         <v>2771068</v>
       </c>
@@ -3274,40 +3289,40 @@
         <v>2024</v>
       </c>
       <c r="H4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="T4">
         <v>0</v>
       </c>
-      <c r="W4" t="s">
-        <v>32</v>
-      </c>
-      <c r="X4" t="s">
-        <v>46</v>
-      </c>
       <c r="Y4" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="Z4" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="AA4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AB4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30">
       <c r="A5">
         <v>2771439</v>
       </c>
@@ -3330,40 +3345,40 @@
         <v>2024</v>
       </c>
       <c r="H5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="I5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="T5">
         <v>0</v>
       </c>
-      <c r="W5" t="s">
-        <v>32</v>
-      </c>
-      <c r="X5" t="s">
-        <v>53</v>
-      </c>
       <c r="Y5" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="Z5" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="AA5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AB5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>57</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30">
       <c r="A6">
         <v>2771923</v>
       </c>
@@ -3386,37 +3401,37 @@
         <v>2024</v>
       </c>
       <c r="H6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="T6">
         <v>0</v>
       </c>
-      <c r="W6" t="s">
-        <v>32</v>
-      </c>
-      <c r="X6" t="s">
-        <v>59</v>
-      </c>
       <c r="Y6" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="Z6" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="AA6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AB6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:30">
       <c r="A7">
         <v>2772237</v>
       </c>
@@ -3439,40 +3454,40 @@
         <v>2024</v>
       </c>
       <c r="H7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="T7">
         <v>0</v>
       </c>
-      <c r="W7" t="s">
-        <v>32</v>
-      </c>
-      <c r="X7" t="s">
-        <v>66</v>
-      </c>
       <c r="Y7" t="s">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="Z7" t="s">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="AA7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AB7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>70</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30">
       <c r="A8">
         <v>2772563</v>
       </c>
@@ -3495,40 +3510,40 @@
         <v>2024</v>
       </c>
       <c r="H8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J8" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T8">
         <v>0</v>
       </c>
-      <c r="W8" t="s">
-        <v>32</v>
-      </c>
-      <c r="X8" t="s">
-        <v>73</v>
-      </c>
       <c r="Y8" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="Z8" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="AA8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AB8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30">
       <c r="A9">
         <v>2772919</v>
       </c>
@@ -3551,37 +3566,37 @@
         <v>2024</v>
       </c>
       <c r="H9" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="T9">
         <v>0</v>
       </c>
-      <c r="W9" t="s">
-        <v>32</v>
-      </c>
-      <c r="X9" t="s">
-        <v>79</v>
-      </c>
       <c r="Y9" t="s">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="Z9" t="s">
-        <v>35</v>
+        <v>81</v>
       </c>
       <c r="AA9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AB9" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="10" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>83</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30">
       <c r="A10">
         <v>2773268</v>
       </c>
@@ -3604,37 +3619,37 @@
         <v>2024</v>
       </c>
       <c r="H10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J10" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="T10">
         <v>0</v>
       </c>
-      <c r="W10" t="s">
-        <v>32</v>
-      </c>
-      <c r="X10" t="s">
-        <v>85</v>
-      </c>
       <c r="Y10" t="s">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c r="Z10" t="s">
-        <v>35</v>
+        <v>87</v>
       </c>
       <c r="AA10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AB10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>89</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30">
       <c r="A11">
         <v>2773855</v>
       </c>
@@ -3657,40 +3672,40 @@
         <v>2024</v>
       </c>
       <c r="H11" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I11" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="J11" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K11" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="T11">
         <v>0</v>
       </c>
-      <c r="W11" t="s">
-        <v>32</v>
-      </c>
-      <c r="X11" t="s">
-        <v>92</v>
-      </c>
       <c r="Y11" t="s">
-        <v>93</v>
+        <v>34</v>
       </c>
       <c r="Z11" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="AA11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AB11" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>96</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:30">
       <c r="A12">
         <v>2774227</v>
       </c>
@@ -3713,37 +3728,37 @@
         <v>2024</v>
       </c>
       <c r="H12" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I12" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="K12" t="s">
-        <v>98</v>
-      </c>
-      <c r="W12" t="s">
-        <v>32</v>
-      </c>
-      <c r="X12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Y12" t="s">
-        <v>100</v>
+        <v>34</v>
       </c>
       <c r="Z12" t="s">
-        <v>35</v>
+        <v>101</v>
       </c>
       <c r="AA12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AB12" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30">
       <c r="A13">
         <v>2774826</v>
       </c>
@@ -3766,40 +3781,40 @@
         <v>2024</v>
       </c>
       <c r="H13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I13" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="J13" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K13" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="T13">
         <v>0</v>
       </c>
-      <c r="W13" t="s">
-        <v>32</v>
-      </c>
-      <c r="X13" t="s">
-        <v>105</v>
-      </c>
       <c r="Y13" t="s">
-        <v>106</v>
+        <v>34</v>
       </c>
       <c r="Z13" t="s">
-        <v>35</v>
+        <v>107</v>
       </c>
       <c r="AA13" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AB13" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="14" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>109</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30">
       <c r="A14">
         <v>2775148</v>
       </c>
@@ -3822,46 +3837,46 @@
         <v>2024</v>
       </c>
       <c r="H14" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="I14" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="J14" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="K14" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="T14">
         <v>0</v>
       </c>
-      <c r="U14">
+      <c r="W14">
         <v>1</v>
       </c>
-      <c r="V14">
+      <c r="X14">
         <v>1</v>
       </c>
-      <c r="W14" t="s">
-        <v>32</v>
-      </c>
-      <c r="X14" t="s">
-        <v>112</v>
-      </c>
       <c r="Y14" t="s">
-        <v>113</v>
+        <v>34</v>
       </c>
       <c r="Z14" t="s">
-        <v>35</v>
+        <v>114</v>
       </c>
       <c r="AA14" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AB14" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="15" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>116</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30">
       <c r="A15">
         <v>2775664</v>
       </c>
@@ -3884,37 +3899,37 @@
         <v>2024</v>
       </c>
       <c r="H15" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I15" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="J15" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="T15">
         <v>0</v>
       </c>
-      <c r="W15" t="s">
-        <v>32</v>
-      </c>
-      <c r="X15" t="s">
-        <v>118</v>
-      </c>
       <c r="Y15" t="s">
-        <v>119</v>
+        <v>34</v>
       </c>
       <c r="Z15" t="s">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="AA15" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AB15" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>122</v>
+      </c>
+      <c r="AD15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30">
       <c r="A16">
         <v>2776114</v>
       </c>
@@ -3937,40 +3952,40 @@
         <v>2024</v>
       </c>
       <c r="H16" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I16" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J16" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K16" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="T16">
         <v>0</v>
       </c>
-      <c r="W16" t="s">
-        <v>32</v>
-      </c>
-      <c r="X16" t="s">
-        <v>124</v>
-      </c>
       <c r="Y16" t="s">
-        <v>125</v>
+        <v>34</v>
       </c>
       <c r="Z16" t="s">
-        <v>35</v>
+        <v>126</v>
       </c>
       <c r="AA16" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AB16" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="17" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:30">
       <c r="A17">
         <v>2776541</v>
       </c>
@@ -3993,40 +4008,40 @@
         <v>2024</v>
       </c>
       <c r="H17" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="I17" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="J17" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="K17" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="T17">
         <v>0</v>
       </c>
-      <c r="W17" t="s">
-        <v>32</v>
-      </c>
-      <c r="X17" t="s">
-        <v>131</v>
-      </c>
       <c r="Y17" t="s">
-        <v>132</v>
+        <v>34</v>
       </c>
       <c r="Z17" t="s">
-        <v>35</v>
+        <v>133</v>
       </c>
       <c r="AA17" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AB17" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="18" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>135</v>
+      </c>
+      <c r="AD17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:30">
       <c r="A18">
         <v>2777087</v>
       </c>
@@ -4049,40 +4064,40 @@
         <v>2024</v>
       </c>
       <c r="H18" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="J18" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="K18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="T18">
         <v>0</v>
       </c>
-      <c r="W18" t="s">
-        <v>32</v>
-      </c>
-      <c r="X18" t="s">
-        <v>138</v>
-      </c>
       <c r="Y18" t="s">
-        <v>139</v>
+        <v>34</v>
       </c>
       <c r="Z18" t="s">
-        <v>35</v>
+        <v>140</v>
       </c>
       <c r="AA18" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AB18" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="19" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>142</v>
+      </c>
+      <c r="AD18" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:30">
       <c r="A19">
         <v>2777535</v>
       </c>
@@ -4105,37 +4120,37 @@
         <v>2024</v>
       </c>
       <c r="H19" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="I19" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="J19" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="T19">
         <v>0</v>
       </c>
-      <c r="W19" t="s">
-        <v>32</v>
-      </c>
-      <c r="X19" t="s">
-        <v>144</v>
-      </c>
       <c r="Y19" t="s">
-        <v>145</v>
+        <v>34</v>
       </c>
       <c r="Z19" t="s">
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="AA19" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AB19" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="20" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>148</v>
+      </c>
+      <c r="AD19" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:30">
       <c r="A20">
         <v>2778373</v>
       </c>
@@ -4158,40 +4173,40 @@
         <v>2024</v>
       </c>
       <c r="H20" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I20" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J20" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="K20" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="T20">
         <v>0</v>
       </c>
-      <c r="W20" t="s">
-        <v>32</v>
-      </c>
-      <c r="X20" t="s">
-        <v>151</v>
-      </c>
       <c r="Y20" t="s">
-        <v>152</v>
+        <v>34</v>
       </c>
       <c r="Z20" t="s">
-        <v>35</v>
+        <v>153</v>
       </c>
       <c r="AA20" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AB20" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="21" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>155</v>
+      </c>
+      <c r="AD20" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:30">
       <c r="A21">
         <v>2778967</v>
       </c>
@@ -4214,46 +4229,46 @@
         <v>2024</v>
       </c>
       <c r="H21" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="I21" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="J21" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="K21" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="T21">
         <v>0</v>
       </c>
-      <c r="U21">
+      <c r="W21">
         <v>1</v>
       </c>
-      <c r="V21">
+      <c r="X21">
         <v>1</v>
       </c>
-      <c r="W21" t="s">
-        <v>32</v>
-      </c>
-      <c r="X21" t="s">
-        <v>158</v>
-      </c>
       <c r="Y21" t="s">
-        <v>159</v>
+        <v>34</v>
       </c>
       <c r="Z21" t="s">
-        <v>35</v>
+        <v>160</v>
       </c>
       <c r="AA21" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AB21" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="22" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>162</v>
+      </c>
+      <c r="AD21" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" spans="1:30">
       <c r="A22">
         <v>2779730</v>
       </c>
@@ -4276,37 +4291,37 @@
         <v>2024</v>
       </c>
       <c r="H22" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="I22" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="J22" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="K22" t="s">
-        <v>164</v>
-      </c>
-      <c r="W22" t="s">
-        <v>32</v>
-      </c>
-      <c r="X22" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Y22" t="s">
-        <v>166</v>
+        <v>34</v>
       </c>
       <c r="Z22" t="s">
-        <v>35</v>
+        <v>167</v>
       </c>
       <c r="AA22" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AB22" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="23" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>169</v>
+      </c>
+      <c r="AD22" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23" spans="1:30">
       <c r="A23">
         <v>2780333</v>
       </c>
@@ -4329,40 +4344,40 @@
         <v>2024</v>
       </c>
       <c r="H23" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I23" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="J23" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="K23" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="T23">
         <v>0</v>
       </c>
-      <c r="W23" t="s">
-        <v>32</v>
-      </c>
-      <c r="X23" t="s">
-        <v>172</v>
-      </c>
       <c r="Y23" t="s">
-        <v>173</v>
+        <v>34</v>
       </c>
       <c r="Z23" t="s">
-        <v>35</v>
+        <v>174</v>
       </c>
       <c r="AA23" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AB23" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="24" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC23" t="s">
+        <v>176</v>
+      </c>
+      <c r="AD23" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24" spans="1:30">
       <c r="A24">
         <v>2780945</v>
       </c>
@@ -4385,40 +4400,40 @@
         <v>2024</v>
       </c>
       <c r="H24" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="I24" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="J24" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="K24" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="T24">
         <v>0</v>
       </c>
-      <c r="W24" t="s">
-        <v>32</v>
-      </c>
-      <c r="X24" t="s">
-        <v>179</v>
-      </c>
       <c r="Y24" t="s">
-        <v>180</v>
+        <v>34</v>
       </c>
       <c r="Z24" t="s">
-        <v>35</v>
+        <v>181</v>
       </c>
       <c r="AA24" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AB24" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="25" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC24" t="s">
+        <v>183</v>
+      </c>
+      <c r="AD24" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25" spans="1:30">
       <c r="A25">
         <v>2781549</v>
       </c>
@@ -4441,40 +4456,40 @@
         <v>2024</v>
       </c>
       <c r="H25" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="I25" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="J25" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="K25" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="T25">
         <v>0</v>
       </c>
-      <c r="W25" t="s">
-        <v>32</v>
-      </c>
-      <c r="X25" t="s">
-        <v>186</v>
-      </c>
       <c r="Y25" t="s">
-        <v>187</v>
+        <v>34</v>
       </c>
       <c r="Z25" t="s">
-        <v>35</v>
+        <v>188</v>
       </c>
       <c r="AA25" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AB25" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="26" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC25" t="s">
+        <v>190</v>
+      </c>
+      <c r="AD25" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="26" spans="1:30">
       <c r="A26">
         <v>2782239</v>
       </c>
@@ -4497,37 +4512,37 @@
         <v>2024</v>
       </c>
       <c r="H26" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I26" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="J26" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="T26">
         <v>0</v>
       </c>
-      <c r="W26" t="s">
-        <v>32</v>
-      </c>
-      <c r="X26" t="s">
-        <v>192</v>
-      </c>
       <c r="Y26" t="s">
-        <v>193</v>
+        <v>34</v>
       </c>
       <c r="Z26" t="s">
-        <v>35</v>
+        <v>194</v>
       </c>
       <c r="AA26" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AB26" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="27" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC26" t="s">
+        <v>196</v>
+      </c>
+      <c r="AD26" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="27" spans="1:30">
       <c r="A27">
         <v>2782869</v>
       </c>
@@ -4550,40 +4565,40 @@
         <v>2024</v>
       </c>
       <c r="H27" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="I27" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="J27" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K27" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="T27">
         <v>0</v>
       </c>
-      <c r="W27" t="s">
-        <v>32</v>
-      </c>
-      <c r="X27" t="s">
-        <v>199</v>
-      </c>
       <c r="Y27" t="s">
-        <v>200</v>
+        <v>34</v>
       </c>
       <c r="Z27" t="s">
-        <v>35</v>
+        <v>201</v>
       </c>
       <c r="AA27" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AB27" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="28" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC27" t="s">
+        <v>203</v>
+      </c>
+      <c r="AD27" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="28" spans="1:30">
       <c r="A28">
         <v>2783535</v>
       </c>
@@ -4606,46 +4621,46 @@
         <v>2024</v>
       </c>
       <c r="H28" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="I28" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="J28" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K28" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="T28">
         <v>0</v>
       </c>
-      <c r="U28">
+      <c r="W28">
         <v>3</v>
       </c>
-      <c r="V28">
+      <c r="X28">
         <v>3</v>
       </c>
-      <c r="W28" t="s">
-        <v>32</v>
-      </c>
-      <c r="X28" t="s">
-        <v>206</v>
-      </c>
       <c r="Y28" t="s">
-        <v>207</v>
+        <v>34</v>
       </c>
       <c r="Z28" t="s">
-        <v>35</v>
+        <v>208</v>
       </c>
       <c r="AA28" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AB28" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="29" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC28" t="s">
+        <v>210</v>
+      </c>
+      <c r="AD28" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="29" spans="1:30">
       <c r="A29">
         <v>2784390</v>
       </c>
@@ -4668,40 +4683,40 @@
         <v>2024</v>
       </c>
       <c r="H29" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="I29" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="J29" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K29" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="T29">
         <v>0</v>
       </c>
-      <c r="W29" t="s">
-        <v>32</v>
-      </c>
-      <c r="X29" t="s">
-        <v>213</v>
-      </c>
       <c r="Y29" t="s">
-        <v>214</v>
+        <v>34</v>
       </c>
       <c r="Z29" t="s">
-        <v>35</v>
+        <v>215</v>
       </c>
       <c r="AA29" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AB29" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="30" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC29" t="s">
+        <v>217</v>
+      </c>
+      <c r="AD29" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="30" spans="1:30">
       <c r="A30">
         <v>2785081</v>
       </c>
@@ -4724,40 +4739,40 @@
         <v>2024</v>
       </c>
       <c r="H30" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="I30" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="J30" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K30" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="T30">
         <v>0</v>
       </c>
-      <c r="W30" t="s">
-        <v>32</v>
-      </c>
-      <c r="X30" t="s">
-        <v>220</v>
-      </c>
       <c r="Y30" t="s">
-        <v>221</v>
+        <v>34</v>
       </c>
       <c r="Z30" t="s">
-        <v>35</v>
+        <v>222</v>
       </c>
       <c r="AA30" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AB30" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="31" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC30" t="s">
+        <v>224</v>
+      </c>
+      <c r="AD30" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="31" spans="1:30">
       <c r="A31">
         <v>2785908</v>
       </c>
@@ -4780,37 +4795,37 @@
         <v>2024</v>
       </c>
       <c r="H31" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="I31" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="J31" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K31" t="s">
-        <v>226</v>
-      </c>
-      <c r="W31" t="s">
-        <v>32</v>
-      </c>
-      <c r="X31" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y31" t="s">
-        <v>228</v>
+        <v>34</v>
       </c>
       <c r="Z31" t="s">
-        <v>35</v>
+        <v>229</v>
       </c>
       <c r="AA31" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AB31" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="32" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC31" t="s">
+        <v>231</v>
+      </c>
+      <c r="AD31" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="32" spans="1:30">
       <c r="A32">
         <v>2786599</v>
       </c>
@@ -4833,46 +4848,46 @@
         <v>2024</v>
       </c>
       <c r="H32" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="I32" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="J32" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K32" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="T32">
         <v>0</v>
       </c>
-      <c r="U32">
+      <c r="W32">
         <v>5</v>
       </c>
-      <c r="V32">
+      <c r="X32">
         <v>5</v>
       </c>
-      <c r="W32" t="s">
-        <v>32</v>
-      </c>
-      <c r="X32" t="s">
-        <v>234</v>
-      </c>
       <c r="Y32" t="s">
-        <v>235</v>
+        <v>34</v>
       </c>
       <c r="Z32" t="s">
-        <v>35</v>
+        <v>236</v>
       </c>
       <c r="AA32" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AB32" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="33" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC32" t="s">
+        <v>238</v>
+      </c>
+      <c r="AD32" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="33" spans="1:30">
       <c r="A33">
         <v>2787239</v>
       </c>
@@ -4895,40 +4910,40 @@
         <v>2024</v>
       </c>
       <c r="H33" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="I33" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="J33" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="K33" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="T33">
         <v>0</v>
       </c>
-      <c r="W33" t="s">
-        <v>32</v>
-      </c>
-      <c r="X33" t="s">
-        <v>241</v>
-      </c>
       <c r="Y33" t="s">
-        <v>242</v>
+        <v>34</v>
       </c>
       <c r="Z33" t="s">
-        <v>35</v>
+        <v>243</v>
       </c>
       <c r="AA33" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AB33" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="34" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC33" t="s">
+        <v>245</v>
+      </c>
+      <c r="AD33" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="34" spans="1:30">
       <c r="A34">
         <v>2787965</v>
       </c>
@@ -4951,40 +4966,40 @@
         <v>2024</v>
       </c>
       <c r="H34" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="I34" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="J34" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K34" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="T34">
         <v>0</v>
       </c>
-      <c r="W34" t="s">
-        <v>32</v>
-      </c>
-      <c r="X34" t="s">
-        <v>248</v>
-      </c>
       <c r="Y34" t="s">
-        <v>249</v>
+        <v>34</v>
       </c>
       <c r="Z34" t="s">
-        <v>35</v>
+        <v>250</v>
       </c>
       <c r="AA34" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AB34" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="35" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC34" t="s">
+        <v>252</v>
+      </c>
+      <c r="AD34" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="35" spans="1:30">
       <c r="A35">
         <v>2788781</v>
       </c>
@@ -5007,43 +5022,43 @@
         <v>2024</v>
       </c>
       <c r="H35" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="I35" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="J35" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="K35" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="T35">
         <v>0</v>
       </c>
-      <c r="U35">
+      <c r="W35">
         <v>1</v>
       </c>
-      <c r="V35">
+      <c r="X35">
         <v>1</v>
       </c>
-      <c r="W35" t="s">
-        <v>32</v>
-      </c>
-      <c r="X35" t="s">
-        <v>255</v>
-      </c>
       <c r="Y35" t="s">
-        <v>256</v>
+        <v>34</v>
       </c>
       <c r="Z35" t="s">
-        <v>35</v>
+        <v>257</v>
       </c>
       <c r="AA35" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="36" spans="1:28">
+        <v>258</v>
+      </c>
+      <c r="AB35" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC35" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="36" spans="1:30">
       <c r="A36">
         <v>2789812</v>
       </c>
@@ -5066,40 +5081,40 @@
         <v>2024</v>
       </c>
       <c r="H36" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="I36" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="J36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K36" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="T36">
         <v>0</v>
       </c>
-      <c r="W36" t="s">
-        <v>32</v>
-      </c>
-      <c r="X36" t="s">
-        <v>261</v>
-      </c>
       <c r="Y36" t="s">
-        <v>262</v>
+        <v>34</v>
       </c>
       <c r="Z36" t="s">
-        <v>35</v>
+        <v>263</v>
       </c>
       <c r="AA36" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AB36" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="37" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC36" t="s">
+        <v>265</v>
+      </c>
+      <c r="AD36" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="37" spans="1:30">
       <c r="A37">
         <v>2790833</v>
       </c>
@@ -5122,40 +5137,40 @@
         <v>2024</v>
       </c>
       <c r="H37" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="I37" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="J37" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K37" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="T37">
         <v>0</v>
       </c>
-      <c r="W37" t="s">
-        <v>32</v>
-      </c>
-      <c r="X37" t="s">
-        <v>268</v>
-      </c>
       <c r="Y37" t="s">
-        <v>269</v>
+        <v>34</v>
       </c>
       <c r="Z37" t="s">
-        <v>35</v>
+        <v>270</v>
       </c>
       <c r="AA37" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AB37" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="38" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC37" t="s">
+        <v>272</v>
+      </c>
+      <c r="AD37" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="38" spans="1:30">
       <c r="A38">
         <v>2791871</v>
       </c>
@@ -5178,43 +5193,43 @@
         <v>2024</v>
       </c>
       <c r="H38" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="I38" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="J38" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="K38" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="T38">
         <v>0</v>
       </c>
-      <c r="U38">
-        <v>0</v>
-      </c>
-      <c r="W38" t="s">
-        <v>32</v>
-      </c>
-      <c r="X38" t="s">
-        <v>275</v>
+      <c r="W38">
+        <v>0</v>
       </c>
       <c r="Y38" t="s">
-        <v>276</v>
+        <v>34</v>
       </c>
       <c r="Z38" t="s">
-        <v>35</v>
+        <v>277</v>
       </c>
       <c r="AA38" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AB38" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="39" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC38" t="s">
+        <v>279</v>
+      </c>
+      <c r="AD38" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:30">
       <c r="A39">
         <v>2792706</v>
       </c>
@@ -5237,40 +5252,40 @@
         <v>2024</v>
       </c>
       <c r="H39" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="I39" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="J39" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="K39" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="T39">
         <v>0</v>
       </c>
-      <c r="W39" t="s">
-        <v>32</v>
-      </c>
-      <c r="X39" t="s">
-        <v>282</v>
-      </c>
       <c r="Y39" t="s">
-        <v>283</v>
+        <v>34</v>
       </c>
       <c r="Z39" t="s">
-        <v>35</v>
+        <v>284</v>
       </c>
       <c r="AA39" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AB39" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="40" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC39" t="s">
+        <v>286</v>
+      </c>
+      <c r="AD39" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="40" spans="1:30">
       <c r="A40">
         <v>2793431</v>
       </c>
@@ -5293,37 +5308,37 @@
         <v>2024</v>
       </c>
       <c r="H40" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="I40" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="J40" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="K40" t="s">
-        <v>288</v>
-      </c>
-      <c r="W40" t="s">
-        <v>32</v>
-      </c>
-      <c r="X40" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Y40" t="s">
-        <v>290</v>
+        <v>34</v>
       </c>
       <c r="Z40" t="s">
-        <v>35</v>
+        <v>291</v>
       </c>
       <c r="AA40" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AB40" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="41" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC40" t="s">
+        <v>293</v>
+      </c>
+      <c r="AD40" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="41" spans="1:30">
       <c r="A41">
         <v>2794507</v>
       </c>
@@ -5346,40 +5361,40 @@
         <v>2024</v>
       </c>
       <c r="H41" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="I41" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="J41" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="K41" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="T41">
         <v>0</v>
       </c>
-      <c r="W41" t="s">
-        <v>32</v>
-      </c>
-      <c r="X41" t="s">
-        <v>296</v>
-      </c>
       <c r="Y41" t="s">
-        <v>297</v>
+        <v>34</v>
       </c>
       <c r="Z41" t="s">
-        <v>35</v>
+        <v>298</v>
       </c>
       <c r="AA41" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AB41" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="42" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC41" t="s">
+        <v>300</v>
+      </c>
+      <c r="AD41" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="42" spans="1:30">
       <c r="A42">
         <v>2795703</v>
       </c>
@@ -5402,43 +5417,43 @@
         <v>2024</v>
       </c>
       <c r="H42" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="I42" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="J42" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="K42" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="T42">
         <v>0</v>
       </c>
-      <c r="U42">
+      <c r="W42">
         <v>8</v>
       </c>
-      <c r="W42" t="s">
-        <v>32</v>
-      </c>
-      <c r="X42" t="s">
-        <v>303</v>
-      </c>
       <c r="Y42" t="s">
-        <v>304</v>
+        <v>34</v>
       </c>
       <c r="Z42" t="s">
-        <v>35</v>
+        <v>305</v>
       </c>
       <c r="AA42" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AB42" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="43" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC42" t="s">
+        <v>307</v>
+      </c>
+      <c r="AD42" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="43" spans="1:30">
       <c r="A43">
         <v>2796729</v>
       </c>
@@ -5461,40 +5476,40 @@
         <v>2024</v>
       </c>
       <c r="H43" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="I43" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="J43" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="K43" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="T43">
         <v>0</v>
       </c>
-      <c r="W43" t="s">
-        <v>32</v>
-      </c>
-      <c r="X43" t="s">
-        <v>310</v>
-      </c>
       <c r="Y43" t="s">
-        <v>311</v>
+        <v>34</v>
       </c>
       <c r="Z43" t="s">
-        <v>35</v>
+        <v>312</v>
       </c>
       <c r="AA43" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AB43" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="44" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC43" t="s">
+        <v>314</v>
+      </c>
+      <c r="AD43" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="44" spans="1:30">
       <c r="A44">
         <v>2798059</v>
       </c>
@@ -5517,40 +5532,40 @@
         <v>2024</v>
       </c>
       <c r="H44" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="I44" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="J44" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="K44" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="T44">
         <v>0</v>
       </c>
-      <c r="W44" t="s">
-        <v>32</v>
-      </c>
-      <c r="X44" t="s">
-        <v>317</v>
-      </c>
       <c r="Y44" t="s">
-        <v>318</v>
+        <v>34</v>
       </c>
       <c r="Z44" t="s">
-        <v>35</v>
+        <v>319</v>
       </c>
       <c r="AA44" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AB44" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="45" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC44" t="s">
+        <v>321</v>
+      </c>
+      <c r="AD44" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="45" spans="1:30">
       <c r="A45">
         <v>2799827</v>
       </c>
@@ -5573,40 +5588,40 @@
         <v>2024</v>
       </c>
       <c r="H45" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="I45" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="J45" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K45" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="T45">
         <v>0</v>
       </c>
-      <c r="W45" t="s">
-        <v>32</v>
-      </c>
-      <c r="X45" t="s">
-        <v>324</v>
-      </c>
       <c r="Y45" t="s">
-        <v>325</v>
+        <v>34</v>
       </c>
       <c r="Z45" t="s">
-        <v>35</v>
+        <v>326</v>
       </c>
       <c r="AA45" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AB45" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="46" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC45" t="s">
+        <v>328</v>
+      </c>
+      <c r="AD45" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="46" spans="1:30">
       <c r="A46">
         <v>2801528</v>
       </c>
@@ -5629,43 +5644,43 @@
         <v>2024</v>
       </c>
       <c r="H46" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="I46" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="J46" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="K46" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="T46">
         <v>0</v>
       </c>
-      <c r="U46">
-        <v>0</v>
-      </c>
-      <c r="W46" t="s">
-        <v>32</v>
-      </c>
-      <c r="X46" t="s">
-        <v>331</v>
+      <c r="W46">
+        <v>0</v>
       </c>
       <c r="Y46" t="s">
-        <v>332</v>
+        <v>34</v>
       </c>
       <c r="Z46" t="s">
-        <v>35</v>
+        <v>333</v>
       </c>
       <c r="AA46" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AB46" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="47" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC46" t="s">
+        <v>335</v>
+      </c>
+      <c r="AD46" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="47" spans="1:30">
       <c r="A47">
         <v>2803539</v>
       </c>
@@ -5688,43 +5703,43 @@
         <v>2024</v>
       </c>
       <c r="H47" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="I47" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J47" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="K47" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="T47">
         <v>0</v>
       </c>
-      <c r="U47">
-        <v>0</v>
-      </c>
-      <c r="W47" t="s">
-        <v>32</v>
-      </c>
-      <c r="X47" t="s">
-        <v>338</v>
+      <c r="W47">
+        <v>0</v>
       </c>
       <c r="Y47" t="s">
-        <v>339</v>
+        <v>34</v>
       </c>
       <c r="Z47" t="s">
-        <v>35</v>
+        <v>340</v>
       </c>
       <c r="AA47" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AB47" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="48" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC47" t="s">
+        <v>342</v>
+      </c>
+      <c r="AD47" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="48" spans="1:30">
       <c r="A48">
         <v>2805111</v>
       </c>
@@ -5747,40 +5762,40 @@
         <v>2024</v>
       </c>
       <c r="H48" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="I48" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="J48" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K48" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="T48">
         <v>0</v>
       </c>
-      <c r="W48" t="s">
-        <v>32</v>
-      </c>
-      <c r="X48" t="s">
-        <v>345</v>
-      </c>
       <c r="Y48" t="s">
-        <v>346</v>
+        <v>34</v>
       </c>
       <c r="Z48" t="s">
-        <v>35</v>
+        <v>347</v>
       </c>
       <c r="AA48" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AB48" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="49" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC48" t="s">
+        <v>349</v>
+      </c>
+      <c r="AD48" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="49" spans="1:30">
       <c r="A49">
         <v>2806964</v>
       </c>
@@ -5803,43 +5818,43 @@
         <v>2024</v>
       </c>
       <c r="H49" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="I49" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="J49" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="T49">
         <v>0</v>
       </c>
-      <c r="U49">
+      <c r="W49">
         <v>18</v>
       </c>
-      <c r="V49">
+      <c r="X49">
         <v>18</v>
       </c>
-      <c r="W49" t="s">
-        <v>32</v>
-      </c>
-      <c r="X49" t="s">
-        <v>351</v>
-      </c>
       <c r="Y49" t="s">
-        <v>352</v>
+        <v>34</v>
       </c>
       <c r="Z49" t="s">
-        <v>35</v>
+        <v>353</v>
       </c>
       <c r="AA49" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AB49" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="50" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC49" t="s">
+        <v>355</v>
+      </c>
+      <c r="AD49" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="50" spans="1:30">
       <c r="A50">
         <v>2808713</v>
       </c>
@@ -5862,43 +5877,43 @@
         <v>2024</v>
       </c>
       <c r="H50" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="I50" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="J50" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K50" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="T50">
         <v>0</v>
       </c>
-      <c r="U50">
-        <v>0</v>
-      </c>
-      <c r="W50" t="s">
-        <v>32</v>
-      </c>
-      <c r="X50" t="s">
-        <v>358</v>
+      <c r="W50">
+        <v>0</v>
       </c>
       <c r="Y50" t="s">
-        <v>359</v>
+        <v>34</v>
       </c>
       <c r="Z50" t="s">
-        <v>35</v>
+        <v>360</v>
       </c>
       <c r="AA50" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AB50" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="51" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC50" t="s">
+        <v>362</v>
+      </c>
+      <c r="AD50" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="51" spans="1:30">
       <c r="A51">
         <v>2810337</v>
       </c>
@@ -5921,43 +5936,43 @@
         <v>2024</v>
       </c>
       <c r="H51" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="I51" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="J51" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="K51" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="T51">
         <v>0</v>
       </c>
-      <c r="U51">
-        <v>0</v>
-      </c>
-      <c r="W51" t="s">
-        <v>32</v>
-      </c>
-      <c r="X51" t="s">
-        <v>365</v>
+      <c r="W51">
+        <v>0</v>
       </c>
       <c r="Y51" t="s">
-        <v>366</v>
+        <v>34</v>
       </c>
       <c r="Z51" t="s">
-        <v>35</v>
+        <v>367</v>
       </c>
       <c r="AA51" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AB51" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="52" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC51" t="s">
+        <v>369</v>
+      </c>
+      <c r="AD51" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="52" spans="1:30">
       <c r="A52">
         <v>2811912</v>
       </c>
@@ -5980,40 +5995,40 @@
         <v>2024</v>
       </c>
       <c r="H52" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="I52" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="J52" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="K52" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="T52">
         <v>0</v>
       </c>
-      <c r="W52" t="s">
-        <v>32</v>
-      </c>
-      <c r="X52" t="s">
-        <v>372</v>
-      </c>
       <c r="Y52" t="s">
-        <v>373</v>
+        <v>34</v>
       </c>
       <c r="Z52" t="s">
-        <v>35</v>
+        <v>374</v>
       </c>
       <c r="AA52" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AB52" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="53" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC52" t="s">
+        <v>376</v>
+      </c>
+      <c r="AD52" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="53" spans="1:30">
       <c r="A53">
         <v>2813446</v>
       </c>
@@ -6036,43 +6051,43 @@
         <v>2024</v>
       </c>
       <c r="H53" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="I53" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="J53" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="K53" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="T53">
         <v>0</v>
       </c>
-      <c r="U53">
-        <v>0</v>
-      </c>
-      <c r="W53" t="s">
-        <v>32</v>
-      </c>
-      <c r="X53" t="s">
-        <v>379</v>
+      <c r="W53">
+        <v>0</v>
       </c>
       <c r="Y53" t="s">
-        <v>380</v>
+        <v>34</v>
       </c>
       <c r="Z53" t="s">
-        <v>35</v>
+        <v>381</v>
       </c>
       <c r="AA53" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AB53" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="54" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC53" t="s">
+        <v>383</v>
+      </c>
+      <c r="AD53" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="54" spans="1:30">
       <c r="A54">
         <v>2815491</v>
       </c>
@@ -6095,16 +6110,16 @@
         <v>2024</v>
       </c>
       <c r="H54" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="I54" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="J54" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="K54" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="P54">
         <v>0</v>
@@ -6112,29 +6127,29 @@
       <c r="T54">
         <v>0</v>
       </c>
-      <c r="U54">
-        <v>0</v>
-      </c>
-      <c r="W54" t="s">
-        <v>32</v>
-      </c>
-      <c r="X54" t="s">
-        <v>386</v>
+      <c r="W54">
+        <v>0</v>
       </c>
       <c r="Y54" t="s">
-        <v>387</v>
+        <v>34</v>
       </c>
       <c r="Z54" t="s">
-        <v>35</v>
+        <v>388</v>
       </c>
       <c r="AA54" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AB54" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="55" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC54" t="s">
+        <v>390</v>
+      </c>
+      <c r="AD54" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="55" spans="1:30">
       <c r="A55">
         <v>2817638</v>
       </c>
@@ -6157,16 +6172,16 @@
         <v>2024</v>
       </c>
       <c r="H55" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="I55" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="J55" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="K55" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="P55">
         <v>0</v>
@@ -6174,29 +6189,29 @@
       <c r="T55">
         <v>0</v>
       </c>
-      <c r="U55">
-        <v>0</v>
-      </c>
-      <c r="W55" t="s">
-        <v>32</v>
-      </c>
-      <c r="X55" t="s">
-        <v>393</v>
+      <c r="W55">
+        <v>0</v>
       </c>
       <c r="Y55" t="s">
-        <v>394</v>
+        <v>34</v>
       </c>
       <c r="Z55" t="s">
-        <v>35</v>
+        <v>395</v>
       </c>
       <c r="AA55" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AB55" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="56" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC55" t="s">
+        <v>397</v>
+      </c>
+      <c r="AD55" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="56" spans="1:30">
       <c r="A56">
         <v>2819284</v>
       </c>
@@ -6219,16 +6234,16 @@
         <v>2024</v>
       </c>
       <c r="H56" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="I56" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="J56" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="K56" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="P56">
         <v>0</v>
@@ -6236,32 +6251,32 @@
       <c r="T56">
         <v>0</v>
       </c>
-      <c r="U56">
+      <c r="W56">
         <v>2</v>
       </c>
-      <c r="V56">
+      <c r="X56">
         <v>2</v>
       </c>
-      <c r="W56" t="s">
-        <v>32</v>
-      </c>
-      <c r="X56" t="s">
-        <v>400</v>
-      </c>
       <c r="Y56" t="s">
-        <v>401</v>
+        <v>34</v>
       </c>
       <c r="Z56" t="s">
-        <v>35</v>
+        <v>402</v>
       </c>
       <c r="AA56" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AB56" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="57" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC56" t="s">
+        <v>404</v>
+      </c>
+      <c r="AD56" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="57" spans="1:30">
       <c r="A57">
         <v>2821022</v>
       </c>
@@ -6284,16 +6299,16 @@
         <v>2024</v>
       </c>
       <c r="H57" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="I57" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="J57" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="K57" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="P57">
         <v>0</v>
@@ -6301,26 +6316,26 @@
       <c r="T57">
         <v>0</v>
       </c>
-      <c r="W57" t="s">
-        <v>32</v>
-      </c>
-      <c r="X57" t="s">
-        <v>407</v>
-      </c>
       <c r="Y57" t="s">
-        <v>408</v>
+        <v>34</v>
       </c>
       <c r="Z57" t="s">
-        <v>35</v>
+        <v>409</v>
       </c>
       <c r="AA57" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AB57" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="58" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC57" t="s">
+        <v>411</v>
+      </c>
+      <c r="AD57" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="58" spans="1:30">
       <c r="A58">
         <v>2822888</v>
       </c>
@@ -6343,13 +6358,13 @@
         <v>2024</v>
       </c>
       <c r="H58" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="I58" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="J58" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="P58">
         <v>0</v>
@@ -6357,26 +6372,26 @@
       <c r="T58">
         <v>0</v>
       </c>
-      <c r="W58" t="s">
-        <v>32</v>
-      </c>
-      <c r="X58" t="s">
-        <v>413</v>
-      </c>
       <c r="Y58" t="s">
-        <v>414</v>
+        <v>34</v>
       </c>
       <c r="Z58" t="s">
-        <v>35</v>
+        <v>415</v>
       </c>
       <c r="AA58" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AB58" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="59" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC58" t="s">
+        <v>417</v>
+      </c>
+      <c r="AD58" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="59" spans="1:30">
       <c r="A59">
         <v>2825238</v>
       </c>
@@ -6399,16 +6414,16 @@
         <v>2024</v>
       </c>
       <c r="H59" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="I59" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="J59" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="K59" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="P59">
         <v>0</v>
@@ -6416,26 +6431,26 @@
       <c r="T59">
         <v>0</v>
       </c>
-      <c r="W59" t="s">
-        <v>32</v>
-      </c>
-      <c r="X59" t="s">
-        <v>419</v>
-      </c>
       <c r="Y59" t="s">
-        <v>420</v>
+        <v>34</v>
       </c>
       <c r="Z59" t="s">
-        <v>35</v>
+        <v>421</v>
       </c>
       <c r="AA59" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AB59" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="60" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC59" t="s">
+        <v>423</v>
+      </c>
+      <c r="AD59" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="60" spans="1:30">
       <c r="A60">
         <v>2826753</v>
       </c>
@@ -6458,16 +6473,16 @@
         <v>2024</v>
       </c>
       <c r="H60" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="I60" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="J60" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="K60" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="P60">
         <v>0</v>
@@ -6475,26 +6490,26 @@
       <c r="T60">
         <v>0</v>
       </c>
-      <c r="W60" t="s">
-        <v>32</v>
-      </c>
-      <c r="X60" t="s">
-        <v>426</v>
-      </c>
       <c r="Y60" t="s">
-        <v>427</v>
+        <v>34</v>
       </c>
       <c r="Z60" t="s">
-        <v>35</v>
+        <v>428</v>
       </c>
       <c r="AA60" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AB60" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="61" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC60" t="s">
+        <v>430</v>
+      </c>
+      <c r="AD60" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="61" spans="1:30">
       <c r="A61">
         <v>2828186</v>
       </c>
@@ -6517,16 +6532,16 @@
         <v>2024</v>
       </c>
       <c r="H61" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="I61" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="J61" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K61" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="P61">
         <v>0</v>
@@ -6534,29 +6549,29 @@
       <c r="T61">
         <v>0</v>
       </c>
-      <c r="U61">
-        <v>0</v>
-      </c>
-      <c r="W61" t="s">
-        <v>32</v>
-      </c>
-      <c r="X61" t="s">
-        <v>433</v>
+      <c r="W61">
+        <v>0</v>
       </c>
       <c r="Y61" t="s">
-        <v>434</v>
+        <v>34</v>
       </c>
       <c r="Z61" t="s">
-        <v>35</v>
+        <v>435</v>
       </c>
       <c r="AA61" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AB61" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="62" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC61" t="s">
+        <v>437</v>
+      </c>
+      <c r="AD61" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="62" spans="1:30">
       <c r="A62">
         <v>2829796</v>
       </c>
@@ -6579,13 +6594,13 @@
         <v>2024</v>
       </c>
       <c r="H62" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="I62" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="J62" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="P62">
         <v>0</v>
@@ -6593,26 +6608,26 @@
       <c r="T62">
         <v>0</v>
       </c>
-      <c r="U62">
-        <v>0</v>
-      </c>
-      <c r="W62" t="s">
-        <v>32</v>
+      <c r="W62">
+        <v>0</v>
       </c>
       <c r="Y62" t="s">
-        <v>439</v>
-      </c>
-      <c r="Z62" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA62" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AB62" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="63" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC62" t="s">
+        <v>442</v>
+      </c>
+      <c r="AD62" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="63" spans="1:30">
       <c r="A63">
         <v>2831467</v>
       </c>
@@ -6635,16 +6650,16 @@
         <v>2024</v>
       </c>
       <c r="H63" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="I63" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="J63" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="K63" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="P63">
         <v>0</v>
@@ -6652,32 +6667,32 @@
       <c r="T63">
         <v>0</v>
       </c>
-      <c r="U63">
+      <c r="W63">
         <v>12</v>
       </c>
-      <c r="V63">
+      <c r="X63">
         <v>12</v>
       </c>
-      <c r="W63" t="s">
-        <v>32</v>
-      </c>
-      <c r="X63" t="s">
-        <v>445</v>
-      </c>
       <c r="Y63" t="s">
-        <v>446</v>
+        <v>34</v>
       </c>
       <c r="Z63" t="s">
-        <v>35</v>
+        <v>447</v>
       </c>
       <c r="AA63" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AB63" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="64" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC63" t="s">
+        <v>449</v>
+      </c>
+      <c r="AD63" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="64" spans="1:30">
       <c r="A64">
         <v>2833510</v>
       </c>
@@ -6700,16 +6715,16 @@
         <v>2024</v>
       </c>
       <c r="H64" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="I64" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J64" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K64" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="P64">
         <v>0</v>
@@ -6717,29 +6732,29 @@
       <c r="T64">
         <v>0</v>
       </c>
-      <c r="U64">
-        <v>0</v>
-      </c>
-      <c r="W64" t="s">
-        <v>32</v>
-      </c>
-      <c r="X64" t="s">
-        <v>452</v>
+      <c r="W64">
+        <v>0</v>
       </c>
       <c r="Y64" t="s">
-        <v>453</v>
+        <v>34</v>
       </c>
       <c r="Z64" t="s">
-        <v>35</v>
+        <v>454</v>
       </c>
       <c r="AA64" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AB64" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="65" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC64" t="s">
+        <v>456</v>
+      </c>
+      <c r="AD64" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="65" spans="1:30">
       <c r="A65">
         <v>2835263</v>
       </c>
@@ -6762,16 +6777,16 @@
         <v>2024</v>
       </c>
       <c r="H65" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="I65" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="J65" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="K65" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="P65">
         <v>0</v>
@@ -6779,26 +6794,26 @@
       <c r="T65">
         <v>0</v>
       </c>
-      <c r="W65" t="s">
-        <v>32</v>
-      </c>
-      <c r="X65" t="s">
-        <v>459</v>
-      </c>
       <c r="Y65" t="s">
-        <v>460</v>
+        <v>34</v>
       </c>
       <c r="Z65" t="s">
-        <v>35</v>
+        <v>461</v>
       </c>
       <c r="AA65" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AB65" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="66" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC65" t="s">
+        <v>463</v>
+      </c>
+      <c r="AD65" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="66" spans="1:30">
       <c r="A66">
         <v>2836764</v>
       </c>
@@ -6821,16 +6836,16 @@
         <v>2024</v>
       </c>
       <c r="H66" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="I66" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="J66" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="K66" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="P66">
         <v>0</v>
@@ -6838,26 +6853,26 @@
       <c r="T66">
         <v>0</v>
       </c>
-      <c r="W66" t="s">
-        <v>32</v>
-      </c>
-      <c r="X66" t="s">
-        <v>466</v>
-      </c>
       <c r="Y66" t="s">
-        <v>467</v>
+        <v>34</v>
       </c>
       <c r="Z66" t="s">
-        <v>35</v>
+        <v>468</v>
       </c>
       <c r="AA66" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AB66" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="67" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC66" t="s">
+        <v>470</v>
+      </c>
+      <c r="AD66" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="67" spans="1:30">
       <c r="A67">
         <v>2838291</v>
       </c>
@@ -6880,16 +6895,16 @@
         <v>2024</v>
       </c>
       <c r="H67" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="I67" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="J67" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="K67" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="P67">
         <v>0</v>
@@ -6897,26 +6912,26 @@
       <c r="T67">
         <v>0</v>
       </c>
-      <c r="W67" t="s">
-        <v>32</v>
-      </c>
-      <c r="X67" t="s">
-        <v>473</v>
-      </c>
       <c r="Y67" t="s">
-        <v>474</v>
+        <v>34</v>
       </c>
       <c r="Z67" t="s">
-        <v>35</v>
+        <v>475</v>
       </c>
       <c r="AA67" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AB67" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="68" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC67" t="s">
+        <v>477</v>
+      </c>
+      <c r="AD67" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="68" spans="1:30">
       <c r="A68">
         <v>2840270</v>
       </c>
@@ -6939,16 +6954,16 @@
         <v>2024</v>
       </c>
       <c r="H68" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="I68" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="J68" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="K68" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="P68">
         <v>0</v>
@@ -6956,26 +6971,26 @@
       <c r="T68">
         <v>0</v>
       </c>
-      <c r="U68">
-        <v>0</v>
-      </c>
-      <c r="W68" t="s">
-        <v>32</v>
+      <c r="W68">
+        <v>0</v>
       </c>
       <c r="Y68" t="s">
-        <v>480</v>
-      </c>
-      <c r="Z68" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA68" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AB68" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="69" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC68" t="s">
+        <v>483</v>
+      </c>
+      <c r="AD68" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="69" spans="1:30">
       <c r="A69">
         <v>2842324</v>
       </c>
@@ -6998,16 +7013,16 @@
         <v>2024</v>
       </c>
       <c r="H69" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="I69" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="J69" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="K69" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="P69">
         <v>0</v>
@@ -7015,26 +7030,26 @@
       <c r="T69">
         <v>0</v>
       </c>
-      <c r="W69" t="s">
-        <v>32</v>
-      </c>
-      <c r="X69" t="s">
-        <v>486</v>
-      </c>
       <c r="Y69" t="s">
-        <v>487</v>
+        <v>34</v>
       </c>
       <c r="Z69" t="s">
-        <v>35</v>
+        <v>488</v>
       </c>
       <c r="AA69" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AB69" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="70" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC69" t="s">
+        <v>490</v>
+      </c>
+      <c r="AD69" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="70" spans="1:30">
       <c r="A70">
         <v>2844986</v>
       </c>
@@ -7057,16 +7072,16 @@
         <v>2024</v>
       </c>
       <c r="H70" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="I70" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="J70" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="K70" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="P70">
         <v>0</v>
@@ -7074,32 +7089,32 @@
       <c r="T70">
         <v>0</v>
       </c>
-      <c r="U70">
+      <c r="W70">
         <v>7</v>
       </c>
-      <c r="V70">
+      <c r="X70">
         <v>7</v>
       </c>
-      <c r="W70" t="s">
-        <v>32</v>
-      </c>
-      <c r="X70" t="s">
-        <v>493</v>
-      </c>
       <c r="Y70" t="s">
-        <v>494</v>
+        <v>34</v>
       </c>
       <c r="Z70" t="s">
-        <v>35</v>
+        <v>495</v>
       </c>
       <c r="AA70" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AB70" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="71" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC70" t="s">
+        <v>497</v>
+      </c>
+      <c r="AD70" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="71" spans="1:30">
       <c r="A71">
         <v>2846347</v>
       </c>
@@ -7122,16 +7137,16 @@
         <v>2024</v>
       </c>
       <c r="H71" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="I71" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="J71" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="K71" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="P71">
         <v>0</v>
@@ -7139,26 +7154,26 @@
       <c r="T71">
         <v>0</v>
       </c>
-      <c r="W71" t="s">
-        <v>32</v>
-      </c>
-      <c r="X71" t="s">
-        <v>500</v>
-      </c>
       <c r="Y71" t="s">
-        <v>501</v>
+        <v>34</v>
       </c>
       <c r="Z71" t="s">
-        <v>35</v>
+        <v>502</v>
       </c>
       <c r="AA71" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AB71" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="72" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC71" t="s">
+        <v>504</v>
+      </c>
+      <c r="AD71" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="72" spans="1:30">
       <c r="A72">
         <v>2848915</v>
       </c>
@@ -7181,16 +7196,16 @@
         <v>2024</v>
       </c>
       <c r="H72" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="I72" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="J72" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="K72" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="P72">
         <v>0</v>
@@ -7198,26 +7213,26 @@
       <c r="T72">
         <v>0</v>
       </c>
-      <c r="W72" t="s">
-        <v>32</v>
-      </c>
-      <c r="X72" t="s">
-        <v>507</v>
-      </c>
       <c r="Y72" t="s">
-        <v>508</v>
+        <v>34</v>
       </c>
       <c r="Z72" t="s">
-        <v>35</v>
+        <v>509</v>
       </c>
       <c r="AA72" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AB72" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="73" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC72" t="s">
+        <v>511</v>
+      </c>
+      <c r="AD72" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="73" spans="1:30">
       <c r="A73">
         <v>2850643</v>
       </c>
@@ -7240,16 +7255,16 @@
         <v>2024</v>
       </c>
       <c r="H73" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="I73" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="J73" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="K73" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="P73">
         <v>0</v>
@@ -7257,26 +7272,26 @@
       <c r="T73">
         <v>0</v>
       </c>
-      <c r="W73" t="s">
-        <v>32</v>
-      </c>
-      <c r="X73" t="s">
-        <v>514</v>
-      </c>
       <c r="Y73" t="s">
-        <v>515</v>
+        <v>34</v>
       </c>
       <c r="Z73" t="s">
-        <v>35</v>
+        <v>516</v>
       </c>
       <c r="AA73" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AB73" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="74" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC73" t="s">
+        <v>518</v>
+      </c>
+      <c r="AD73" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="74" spans="1:30">
       <c r="A74">
         <v>2852165</v>
       </c>
@@ -7299,37 +7314,37 @@
         <v>2024</v>
       </c>
       <c r="H74" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="I74" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="J74" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="K74" t="s">
-        <v>520</v>
-      </c>
-      <c r="W74" t="s">
-        <v>32</v>
-      </c>
-      <c r="X74" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="Y74" t="s">
-        <v>522</v>
+        <v>34</v>
       </c>
       <c r="Z74" t="s">
-        <v>35</v>
+        <v>523</v>
       </c>
       <c r="AA74" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AB74" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="75" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC74" t="s">
+        <v>525</v>
+      </c>
+      <c r="AD74" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="75" spans="1:30">
       <c r="A75">
         <v>2853395</v>
       </c>
@@ -7352,16 +7367,16 @@
         <v>2024</v>
       </c>
       <c r="H75" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="I75" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="J75" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="K75" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="P75">
         <v>0</v>
@@ -7369,26 +7384,26 @@
       <c r="T75">
         <v>0</v>
       </c>
-      <c r="W75" t="s">
-        <v>32</v>
-      </c>
-      <c r="X75" t="s">
-        <v>528</v>
-      </c>
       <c r="Y75" t="s">
-        <v>529</v>
+        <v>34</v>
       </c>
       <c r="Z75" t="s">
-        <v>35</v>
+        <v>530</v>
       </c>
       <c r="AA75" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AB75" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="76" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC75" t="s">
+        <v>532</v>
+      </c>
+      <c r="AD75" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="76" spans="1:30">
       <c r="A76">
         <v>2855034</v>
       </c>
@@ -7411,16 +7426,16 @@
         <v>2024</v>
       </c>
       <c r="H76" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="I76" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="J76" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="K76" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="P76">
         <v>0</v>
@@ -7428,26 +7443,26 @@
       <c r="T76">
         <v>0</v>
       </c>
-      <c r="W76" t="s">
-        <v>32</v>
-      </c>
-      <c r="X76" t="s">
-        <v>535</v>
-      </c>
       <c r="Y76" t="s">
-        <v>536</v>
+        <v>34</v>
       </c>
       <c r="Z76" t="s">
-        <v>35</v>
+        <v>537</v>
       </c>
       <c r="AA76" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AB76" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="77" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC76" t="s">
+        <v>539</v>
+      </c>
+      <c r="AD76" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="77" spans="1:30">
       <c r="A77">
         <v>2857192</v>
       </c>
@@ -7470,16 +7485,16 @@
         <v>2024</v>
       </c>
       <c r="H77" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="I77" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="J77" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="K77" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="P77">
         <v>0</v>
@@ -7487,26 +7502,26 @@
       <c r="T77">
         <v>0</v>
       </c>
-      <c r="W77" t="s">
-        <v>32</v>
-      </c>
-      <c r="X77" t="s">
-        <v>542</v>
-      </c>
       <c r="Y77" t="s">
-        <v>543</v>
+        <v>34</v>
       </c>
       <c r="Z77" t="s">
-        <v>35</v>
+        <v>544</v>
       </c>
       <c r="AA77" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AB77" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="78" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC77" t="s">
+        <v>546</v>
+      </c>
+      <c r="AD77" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="78" spans="1:30">
       <c r="A78">
         <v>2859205</v>
       </c>
@@ -7529,16 +7544,16 @@
         <v>2024</v>
       </c>
       <c r="H78" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="I78" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="J78" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="K78" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="P78">
         <v>0</v>
@@ -7546,26 +7561,26 @@
       <c r="T78">
         <v>0</v>
       </c>
-      <c r="W78" t="s">
-        <v>32</v>
-      </c>
-      <c r="X78" t="s">
-        <v>549</v>
-      </c>
       <c r="Y78" t="s">
-        <v>550</v>
+        <v>34</v>
       </c>
       <c r="Z78" t="s">
-        <v>35</v>
+        <v>551</v>
       </c>
       <c r="AA78" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AB78" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="79" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC78" t="s">
+        <v>553</v>
+      </c>
+      <c r="AD78" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="79" spans="1:30">
       <c r="A79">
         <v>2860770</v>
       </c>
@@ -7588,16 +7603,16 @@
         <v>2024</v>
       </c>
       <c r="H79" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="I79" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="J79" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K79" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="P79">
         <v>0</v>
@@ -7605,26 +7620,26 @@
       <c r="T79">
         <v>0</v>
       </c>
-      <c r="W79" t="s">
-        <v>32</v>
-      </c>
-      <c r="X79" t="s">
-        <v>555</v>
-      </c>
       <c r="Y79" t="s">
-        <v>556</v>
+        <v>34</v>
       </c>
       <c r="Z79" t="s">
-        <v>35</v>
+        <v>557</v>
       </c>
       <c r="AA79" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AB79" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="80" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC79" t="s">
+        <v>559</v>
+      </c>
+      <c r="AD79" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="80" spans="1:30">
       <c r="A80">
         <v>2862768</v>
       </c>
@@ -7647,16 +7662,16 @@
         <v>2024</v>
       </c>
       <c r="H80" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="I80" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="J80" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="K80" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="P80">
         <v>0</v>
@@ -7664,26 +7679,26 @@
       <c r="T80">
         <v>0</v>
       </c>
-      <c r="W80" t="s">
-        <v>32</v>
-      </c>
-      <c r="X80" t="s">
-        <v>562</v>
-      </c>
       <c r="Y80" t="s">
-        <v>563</v>
+        <v>34</v>
       </c>
       <c r="Z80" t="s">
-        <v>35</v>
+        <v>564</v>
       </c>
       <c r="AA80" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AB80" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="81" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC80" t="s">
+        <v>566</v>
+      </c>
+      <c r="AD80" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="81" spans="1:30">
       <c r="A81">
         <v>2864915</v>
       </c>
@@ -7706,16 +7721,16 @@
         <v>2024</v>
       </c>
       <c r="H81" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="I81" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="J81" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="K81" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="P81">
         <v>0</v>
@@ -7723,26 +7738,26 @@
       <c r="T81">
         <v>0</v>
       </c>
-      <c r="W81" t="s">
-        <v>32</v>
-      </c>
-      <c r="X81" t="s">
-        <v>569</v>
-      </c>
       <c r="Y81" t="s">
-        <v>570</v>
+        <v>34</v>
       </c>
       <c r="Z81" t="s">
-        <v>35</v>
+        <v>571</v>
       </c>
       <c r="AA81" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AB81" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="82" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC81" t="s">
+        <v>573</v>
+      </c>
+      <c r="AD81" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="82" spans="1:30">
       <c r="A82">
         <v>2867712</v>
       </c>
@@ -7765,16 +7780,16 @@
         <v>2024</v>
       </c>
       <c r="H82" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="I82" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="J82" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="K82" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="P82">
         <v>0</v>
@@ -7782,26 +7797,26 @@
       <c r="T82">
         <v>0</v>
       </c>
-      <c r="W82" t="s">
-        <v>32</v>
-      </c>
-      <c r="X82" t="s">
-        <v>576</v>
-      </c>
       <c r="Y82" t="s">
-        <v>577</v>
+        <v>34</v>
       </c>
       <c r="Z82" t="s">
-        <v>35</v>
+        <v>578</v>
       </c>
       <c r="AA82" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AB82" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="83" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC82" t="s">
+        <v>580</v>
+      </c>
+      <c r="AD82" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="83" spans="1:30">
       <c r="A83">
         <v>2871010</v>
       </c>
@@ -7824,16 +7839,16 @@
         <v>2024</v>
       </c>
       <c r="H83" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="I83" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="J83" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="K83" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="P83">
         <v>0</v>
@@ -7841,26 +7856,26 @@
       <c r="T83">
         <v>0</v>
       </c>
-      <c r="W83" t="s">
-        <v>32</v>
-      </c>
-      <c r="X83" t="s">
-        <v>583</v>
-      </c>
       <c r="Y83" t="s">
-        <v>584</v>
+        <v>34</v>
       </c>
       <c r="Z83" t="s">
-        <v>35</v>
+        <v>585</v>
       </c>
       <c r="AA83" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AB83" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="84" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC83" t="s">
+        <v>587</v>
+      </c>
+      <c r="AD83" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="84" spans="1:30">
       <c r="A84">
         <v>2873352</v>
       </c>
@@ -7883,16 +7898,16 @@
         <v>2024</v>
       </c>
       <c r="H84" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="I84" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="J84" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="K84" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="P84">
         <v>0</v>
@@ -7900,32 +7915,32 @@
       <c r="T84">
         <v>0</v>
       </c>
-      <c r="U84">
+      <c r="W84">
         <v>5</v>
       </c>
-      <c r="V84">
+      <c r="X84">
         <v>5</v>
       </c>
-      <c r="W84" t="s">
-        <v>32</v>
-      </c>
-      <c r="X84" t="s">
-        <v>590</v>
-      </c>
       <c r="Y84" t="s">
-        <v>591</v>
+        <v>34</v>
       </c>
       <c r="Z84" t="s">
-        <v>35</v>
+        <v>592</v>
       </c>
       <c r="AA84" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AB84" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="85" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC84" t="s">
+        <v>594</v>
+      </c>
+      <c r="AD84" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="85" spans="1:30">
       <c r="A85">
         <v>2875475</v>
       </c>
@@ -7948,16 +7963,16 @@
         <v>2024</v>
       </c>
       <c r="H85" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="I85" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="J85" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="K85" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="P85">
         <v>0</v>
@@ -7965,26 +7980,26 @@
       <c r="T85">
         <v>0</v>
       </c>
-      <c r="W85" t="s">
-        <v>32</v>
-      </c>
-      <c r="X85" t="s">
-        <v>597</v>
-      </c>
       <c r="Y85" t="s">
-        <v>598</v>
+        <v>34</v>
       </c>
       <c r="Z85" t="s">
-        <v>35</v>
+        <v>599</v>
       </c>
       <c r="AA85" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AB85" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="86" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC85" t="s">
+        <v>601</v>
+      </c>
+      <c r="AD85" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="86" spans="1:30">
       <c r="A86">
         <v>2877715</v>
       </c>
@@ -8007,16 +8022,16 @@
         <v>2024</v>
       </c>
       <c r="H86" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="I86" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="J86" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="K86" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="P86">
         <v>0</v>
@@ -8024,23 +8039,26 @@
       <c r="T86">
         <v>0</v>
       </c>
-      <c r="W86" t="s">
-        <v>32</v>
-      </c>
-      <c r="X86" t="s">
-        <v>604</v>
-      </c>
       <c r="Y86" t="s">
-        <v>605</v>
+        <v>34</v>
       </c>
       <c r="Z86" t="s">
-        <v>35</v>
+        <v>606</v>
       </c>
       <c r="AA86" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="87" spans="1:28">
+        <v>607</v>
+      </c>
+      <c r="AB86" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC86" t="s">
+        <v>608</v>
+      </c>
+      <c r="AD86" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="87" spans="1:30">
       <c r="A87">
         <v>2879272</v>
       </c>
@@ -8063,16 +8081,16 @@
         <v>2024</v>
       </c>
       <c r="H87" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="I87" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="J87" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="K87" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="P87">
         <v>0</v>
@@ -8080,26 +8098,26 @@
       <c r="T87">
         <v>0</v>
       </c>
-      <c r="W87" t="s">
-        <v>32</v>
-      </c>
-      <c r="X87" t="s">
-        <v>610</v>
-      </c>
       <c r="Y87" t="s">
-        <v>611</v>
+        <v>34</v>
       </c>
       <c r="Z87" t="s">
-        <v>35</v>
+        <v>613</v>
       </c>
       <c r="AA87" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="AB87" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="88" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC87" t="s">
+        <v>615</v>
+      </c>
+      <c r="AD87" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="88" spans="1:30">
       <c r="A88">
         <v>2880938</v>
       </c>
@@ -8122,16 +8140,16 @@
         <v>2024</v>
       </c>
       <c r="H88" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="I88" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="J88" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="K88" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="P88">
         <v>0</v>
@@ -8139,26 +8157,26 @@
       <c r="T88">
         <v>0</v>
       </c>
-      <c r="W88" t="s">
-        <v>32</v>
-      </c>
-      <c r="X88" t="s">
-        <v>617</v>
-      </c>
       <c r="Y88" t="s">
-        <v>618</v>
+        <v>34</v>
       </c>
       <c r="Z88" t="s">
-        <v>35</v>
+        <v>620</v>
       </c>
       <c r="AA88" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="AB88" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="89" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC88" t="s">
+        <v>622</v>
+      </c>
+      <c r="AD88" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="89" spans="1:30">
       <c r="A89">
         <v>2883213</v>
       </c>
@@ -8181,16 +8199,16 @@
         <v>2024</v>
       </c>
       <c r="H89" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="I89" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="J89" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="K89" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="P89">
         <v>0</v>
@@ -8198,26 +8216,26 @@
       <c r="T89">
         <v>0</v>
       </c>
-      <c r="W89" t="s">
-        <v>32</v>
-      </c>
-      <c r="X89" t="s">
-        <v>624</v>
-      </c>
       <c r="Y89" t="s">
-        <v>625</v>
+        <v>34</v>
       </c>
       <c r="Z89" t="s">
-        <v>35</v>
+        <v>627</v>
       </c>
       <c r="AA89" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="AB89" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="90" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC89" t="s">
+        <v>629</v>
+      </c>
+      <c r="AD89" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="90" spans="1:30">
       <c r="A90">
         <v>2885819</v>
       </c>
@@ -8240,16 +8258,16 @@
         <v>2024</v>
       </c>
       <c r="H90" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="I90" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="J90" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="K90" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="P90">
         <v>0</v>
@@ -8257,26 +8275,26 @@
       <c r="T90">
         <v>0</v>
       </c>
-      <c r="W90" t="s">
-        <v>32</v>
-      </c>
-      <c r="X90" t="s">
-        <v>631</v>
-      </c>
       <c r="Y90" t="s">
-        <v>632</v>
+        <v>34</v>
       </c>
       <c r="Z90" t="s">
-        <v>35</v>
+        <v>634</v>
       </c>
       <c r="AA90" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="AB90" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="91" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC90" t="s">
+        <v>636</v>
+      </c>
+      <c r="AD90" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="91" spans="1:30">
       <c r="A91">
         <v>2887439</v>
       </c>
@@ -8299,16 +8317,16 @@
         <v>2024</v>
       </c>
       <c r="H91" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="I91" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="J91" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="K91" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="P91">
         <v>0</v>
@@ -8316,32 +8334,32 @@
       <c r="T91">
         <v>0</v>
       </c>
-      <c r="U91">
+      <c r="W91">
         <v>10</v>
       </c>
-      <c r="V91">
+      <c r="X91">
         <v>26</v>
       </c>
-      <c r="W91" t="s">
-        <v>32</v>
-      </c>
-      <c r="X91" t="s">
-        <v>638</v>
-      </c>
       <c r="Y91" t="s">
-        <v>639</v>
+        <v>34</v>
       </c>
       <c r="Z91" t="s">
-        <v>35</v>
+        <v>641</v>
       </c>
       <c r="AA91" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="AB91" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="92" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC91" t="s">
+        <v>643</v>
+      </c>
+      <c r="AD91" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="92" spans="1:30">
       <c r="A92">
         <v>2889290</v>
       </c>
@@ -8364,16 +8382,16 @@
         <v>2024</v>
       </c>
       <c r="H92" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="I92" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="J92" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="K92" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="P92">
         <v>0</v>
@@ -8381,26 +8399,26 @@
       <c r="T92">
         <v>0</v>
       </c>
-      <c r="W92" t="s">
-        <v>32</v>
-      </c>
-      <c r="X92" t="s">
-        <v>645</v>
-      </c>
       <c r="Y92" t="s">
-        <v>646</v>
+        <v>34</v>
       </c>
       <c r="Z92" t="s">
-        <v>35</v>
+        <v>648</v>
       </c>
       <c r="AA92" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="AB92" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="93" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC92" t="s">
+        <v>650</v>
+      </c>
+      <c r="AD92" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="93" spans="1:30">
       <c r="A93">
         <v>2891456</v>
       </c>
@@ -8423,16 +8441,16 @@
         <v>2024</v>
       </c>
       <c r="H93" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="I93" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="J93" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="K93" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="P93">
         <v>0</v>
@@ -8440,26 +8458,26 @@
       <c r="T93">
         <v>0</v>
       </c>
-      <c r="W93" t="s">
-        <v>32</v>
-      </c>
-      <c r="X93" t="s">
-        <v>652</v>
-      </c>
       <c r="Y93" t="s">
-        <v>653</v>
+        <v>34</v>
       </c>
       <c r="Z93" t="s">
-        <v>35</v>
+        <v>655</v>
       </c>
       <c r="AA93" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="AB93" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="94" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC93" t="s">
+        <v>657</v>
+      </c>
+      <c r="AD93" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="94" spans="1:30">
       <c r="A94">
         <v>2894077</v>
       </c>
@@ -8482,16 +8500,16 @@
         <v>2024</v>
       </c>
       <c r="H94" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="I94" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="J94" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="K94" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="P94">
         <v>0</v>
@@ -8499,26 +8517,26 @@
       <c r="T94">
         <v>0</v>
       </c>
-      <c r="W94" t="s">
-        <v>32</v>
-      </c>
-      <c r="X94" t="s">
-        <v>659</v>
-      </c>
       <c r="Y94" t="s">
-        <v>660</v>
+        <v>34</v>
       </c>
       <c r="Z94" t="s">
-        <v>35</v>
+        <v>662</v>
       </c>
       <c r="AA94" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="AB94" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="95" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC94" t="s">
+        <v>664</v>
+      </c>
+      <c r="AD94" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="95" spans="1:30">
       <c r="A95">
         <v>2895920</v>
       </c>
@@ -8541,16 +8559,16 @@
         <v>2024</v>
       </c>
       <c r="H95" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="I95" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="J95" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="K95" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="P95">
         <v>0</v>
@@ -8558,26 +8576,26 @@
       <c r="T95">
         <v>0</v>
       </c>
-      <c r="W95" t="s">
-        <v>32</v>
-      </c>
-      <c r="X95" t="s">
-        <v>666</v>
-      </c>
       <c r="Y95" t="s">
-        <v>667</v>
+        <v>34</v>
       </c>
       <c r="Z95" t="s">
-        <v>35</v>
+        <v>669</v>
       </c>
       <c r="AA95" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="AB95" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="96" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC95" t="s">
+        <v>671</v>
+      </c>
+      <c r="AD95" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="96" spans="1:30">
       <c r="A96">
         <v>2897729</v>
       </c>
@@ -8600,16 +8618,16 @@
         <v>2024</v>
       </c>
       <c r="H96" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="I96" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="J96" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="K96" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="P96">
         <v>0</v>
@@ -8617,26 +8635,26 @@
       <c r="T96">
         <v>0</v>
       </c>
-      <c r="W96" t="s">
-        <v>32</v>
-      </c>
-      <c r="X96" t="s">
-        <v>673</v>
-      </c>
       <c r="Y96" t="s">
-        <v>674</v>
+        <v>34</v>
       </c>
       <c r="Z96" t="s">
-        <v>35</v>
+        <v>676</v>
       </c>
       <c r="AA96" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="AB96" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="97" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC96" t="s">
+        <v>678</v>
+      </c>
+      <c r="AD96" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="97" spans="1:30">
       <c r="A97">
         <v>2899665</v>
       </c>
@@ -8659,16 +8677,16 @@
         <v>2024</v>
       </c>
       <c r="H97" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="I97" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="J97" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="K97" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="P97">
         <v>0</v>
@@ -8676,26 +8694,26 @@
       <c r="T97">
         <v>0</v>
       </c>
-      <c r="W97" t="s">
-        <v>32</v>
-      </c>
-      <c r="X97" t="s">
-        <v>680</v>
-      </c>
       <c r="Y97" t="s">
-        <v>681</v>
+        <v>34</v>
       </c>
       <c r="Z97" t="s">
-        <v>35</v>
+        <v>683</v>
       </c>
       <c r="AA97" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="AB97" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="98" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC97" t="s">
+        <v>685</v>
+      </c>
+      <c r="AD97" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="98" spans="1:30">
       <c r="A98">
         <v>2901239</v>
       </c>
@@ -8718,13 +8736,13 @@
         <v>2024</v>
       </c>
       <c r="H98" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="I98" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="J98" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="P98">
         <v>0</v>
@@ -8732,26 +8750,26 @@
       <c r="T98">
         <v>0</v>
       </c>
-      <c r="W98" t="s">
-        <v>32</v>
-      </c>
-      <c r="X98" t="s">
-        <v>686</v>
-      </c>
       <c r="Y98" t="s">
-        <v>687</v>
+        <v>34</v>
       </c>
       <c r="Z98" t="s">
-        <v>35</v>
+        <v>689</v>
       </c>
       <c r="AA98" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="AB98" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="99" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC98" t="s">
+        <v>691</v>
+      </c>
+      <c r="AD98" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="99" spans="1:30">
       <c r="A99">
         <v>2903137</v>
       </c>
@@ -8774,16 +8792,16 @@
         <v>2024</v>
       </c>
       <c r="H99" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="I99" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="J99" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="K99" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="P99">
         <v>0</v>
@@ -8791,26 +8809,26 @@
       <c r="T99">
         <v>0</v>
       </c>
-      <c r="W99" t="s">
-        <v>32</v>
-      </c>
-      <c r="X99" t="s">
-        <v>693</v>
-      </c>
       <c r="Y99" t="s">
-        <v>694</v>
+        <v>34</v>
       </c>
       <c r="Z99" t="s">
-        <v>35</v>
+        <v>696</v>
       </c>
       <c r="AA99" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="AB99" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="100" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC99" t="s">
+        <v>698</v>
+      </c>
+      <c r="AD99" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="100" spans="1:30">
       <c r="A100">
         <v>2904813</v>
       </c>
@@ -8833,16 +8851,16 @@
         <v>2024</v>
       </c>
       <c r="H100" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="I100" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="J100" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="K100" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="P100">
         <v>0</v>
@@ -8850,26 +8868,26 @@
       <c r="T100">
         <v>0</v>
       </c>
-      <c r="W100" t="s">
-        <v>32</v>
-      </c>
-      <c r="X100" t="s">
-        <v>700</v>
-      </c>
       <c r="Y100" t="s">
-        <v>701</v>
+        <v>34</v>
       </c>
       <c r="Z100" t="s">
-        <v>35</v>
+        <v>703</v>
       </c>
       <c r="AA100" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="AB100" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="101" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC100" t="s">
+        <v>705</v>
+      </c>
+      <c r="AD100" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="101" spans="1:30">
       <c r="A101">
         <v>2906543</v>
       </c>
@@ -8892,16 +8910,16 @@
         <v>2024</v>
       </c>
       <c r="H101" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="I101" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="J101" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="K101" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="P101">
         <v>0</v>
@@ -8909,26 +8927,26 @@
       <c r="T101">
         <v>0</v>
       </c>
-      <c r="W101" t="s">
-        <v>32</v>
-      </c>
-      <c r="X101" t="s">
-        <v>707</v>
-      </c>
       <c r="Y101" t="s">
-        <v>708</v>
+        <v>34</v>
       </c>
       <c r="Z101" t="s">
-        <v>35</v>
+        <v>710</v>
       </c>
       <c r="AA101" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="AB101" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="102" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC101" t="s">
+        <v>712</v>
+      </c>
+      <c r="AD101" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="102" spans="1:30">
       <c r="A102">
         <v>2908948</v>
       </c>
@@ -8951,16 +8969,16 @@
         <v>2024</v>
       </c>
       <c r="H102" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="I102" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="J102" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="K102" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="P102">
         <v>0</v>
@@ -8968,26 +8986,26 @@
       <c r="T102">
         <v>0</v>
       </c>
-      <c r="W102" t="s">
-        <v>32</v>
-      </c>
-      <c r="X102" t="s">
-        <v>714</v>
-      </c>
       <c r="Y102" t="s">
-        <v>715</v>
+        <v>34</v>
       </c>
       <c r="Z102" t="s">
-        <v>35</v>
+        <v>717</v>
       </c>
       <c r="AA102" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="AB102" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="103" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC102" t="s">
+        <v>719</v>
+      </c>
+      <c r="AD102" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="103" spans="1:30">
       <c r="A103">
         <v>2911169</v>
       </c>
@@ -9010,16 +9028,16 @@
         <v>2024</v>
       </c>
       <c r="H103" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="I103" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="J103" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="K103" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="P103">
         <v>0</v>
@@ -9027,23 +9045,23 @@
       <c r="T103">
         <v>0</v>
       </c>
-      <c r="W103" t="s">
-        <v>32</v>
-      </c>
-      <c r="X103" t="s">
-        <v>721</v>
-      </c>
       <c r="Y103" t="s">
-        <v>722</v>
+        <v>34</v>
       </c>
       <c r="Z103" t="s">
-        <v>35</v>
+        <v>724</v>
       </c>
       <c r="AA103" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="104" spans="1:28">
+        <v>725</v>
+      </c>
+      <c r="AB103" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC103" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="104" spans="1:30">
       <c r="A104">
         <v>2913363</v>
       </c>
@@ -9066,16 +9084,16 @@
         <v>2024</v>
       </c>
       <c r="H104" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="I104" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="J104" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="K104" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="P104">
         <v>0</v>
@@ -9083,26 +9101,26 @@
       <c r="T104">
         <v>0</v>
       </c>
-      <c r="W104" t="s">
-        <v>32</v>
-      </c>
-      <c r="X104" t="s">
-        <v>727</v>
-      </c>
       <c r="Y104" t="s">
-        <v>728</v>
+        <v>34</v>
       </c>
       <c r="Z104" t="s">
-        <v>35</v>
+        <v>730</v>
       </c>
       <c r="AA104" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="AB104" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="105" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC104" t="s">
+        <v>732</v>
+      </c>
+      <c r="AD104" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="105" spans="1:30">
       <c r="A105">
         <v>2915593</v>
       </c>
@@ -9125,16 +9143,16 @@
         <v>2024</v>
       </c>
       <c r="H105" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="I105" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="J105" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="K105" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="P105">
         <v>0</v>
@@ -9142,32 +9160,32 @@
       <c r="T105">
         <v>0</v>
       </c>
-      <c r="U105">
+      <c r="W105">
         <v>3</v>
       </c>
-      <c r="V105">
+      <c r="X105">
         <v>4</v>
       </c>
-      <c r="W105" t="s">
-        <v>32</v>
-      </c>
-      <c r="X105" t="s">
-        <v>734</v>
-      </c>
       <c r="Y105" t="s">
-        <v>735</v>
+        <v>34</v>
       </c>
       <c r="Z105" t="s">
-        <v>35</v>
+        <v>737</v>
       </c>
       <c r="AA105" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="AB105" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="106" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC105" t="s">
+        <v>739</v>
+      </c>
+      <c r="AD105" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="106" spans="1:30">
       <c r="A106">
         <v>2917507</v>
       </c>
@@ -9190,16 +9208,16 @@
         <v>2024</v>
       </c>
       <c r="H106" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="I106" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="J106" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="K106" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="P106">
         <v>0</v>
@@ -9207,26 +9225,26 @@
       <c r="T106">
         <v>0</v>
       </c>
-      <c r="W106" t="s">
-        <v>32</v>
-      </c>
-      <c r="X106" t="s">
-        <v>741</v>
-      </c>
       <c r="Y106" t="s">
-        <v>742</v>
+        <v>34</v>
       </c>
       <c r="Z106" t="s">
-        <v>35</v>
+        <v>744</v>
       </c>
       <c r="AA106" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="AB106" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="107" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC106" t="s">
+        <v>746</v>
+      </c>
+      <c r="AD106" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="107" spans="1:30">
       <c r="A107">
         <v>2919327</v>
       </c>
@@ -9249,37 +9267,37 @@
         <v>2024</v>
       </c>
       <c r="H107" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="I107" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="J107" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="K107" t="s">
-        <v>747</v>
-      </c>
-      <c r="W107" t="s">
-        <v>32</v>
-      </c>
-      <c r="X107" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="Y107" t="s">
-        <v>749</v>
+        <v>34</v>
       </c>
       <c r="Z107" t="s">
-        <v>35</v>
+        <v>751</v>
       </c>
       <c r="AA107" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="AB107" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="108" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC107" t="s">
+        <v>753</v>
+      </c>
+      <c r="AD107" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="108" spans="1:30">
       <c r="A108">
         <v>2920763</v>
       </c>
@@ -9302,16 +9320,16 @@
         <v>2024</v>
       </c>
       <c r="H108" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="I108" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="J108" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K108" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="P108">
         <v>0</v>
@@ -9319,26 +9337,26 @@
       <c r="T108">
         <v>0</v>
       </c>
-      <c r="W108" t="s">
-        <v>32</v>
-      </c>
-      <c r="X108" t="s">
-        <v>754</v>
-      </c>
       <c r="Y108" t="s">
-        <v>755</v>
+        <v>34</v>
       </c>
       <c r="Z108" t="s">
-        <v>35</v>
+        <v>757</v>
       </c>
       <c r="AA108" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="AB108" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="109" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC108" t="s">
+        <v>759</v>
+      </c>
+      <c r="AD108" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="109" spans="1:30">
       <c r="A109">
         <v>2922519</v>
       </c>
@@ -9361,16 +9379,16 @@
         <v>2024</v>
       </c>
       <c r="H109" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="I109" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="J109" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K109" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="P109">
         <v>0</v>
@@ -9378,23 +9396,23 @@
       <c r="T109">
         <v>0</v>
       </c>
-      <c r="W109" t="s">
-        <v>32</v>
-      </c>
-      <c r="X109" t="s">
-        <v>760</v>
-      </c>
       <c r="Y109" t="s">
-        <v>761</v>
+        <v>34</v>
       </c>
       <c r="Z109" t="s">
-        <v>35</v>
+        <v>763</v>
       </c>
       <c r="AA109" t="s">
-        <v>761</v>
-      </c>
-    </row>
-    <row r="110" spans="1:28">
+        <v>764</v>
+      </c>
+      <c r="AB109" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC109" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="110" spans="1:30">
       <c r="A110">
         <v>2924094</v>
       </c>
@@ -9417,13 +9435,13 @@
         <v>2024</v>
       </c>
       <c r="H110" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="I110" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="J110" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="P110">
         <v>0</v>
@@ -9431,29 +9449,29 @@
       <c r="T110">
         <v>0</v>
       </c>
-      <c r="U110">
+      <c r="W110">
         <v>5</v>
       </c>
-      <c r="V110">
+      <c r="X110">
         <v>5</v>
       </c>
-      <c r="W110" t="s">
-        <v>32</v>
-      </c>
-      <c r="X110" t="s">
-        <v>765</v>
-      </c>
       <c r="Y110" t="s">
-        <v>766</v>
+        <v>34</v>
       </c>
       <c r="Z110" t="s">
-        <v>35</v>
+        <v>768</v>
       </c>
       <c r="AA110" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="111" spans="1:28">
+        <v>769</v>
+      </c>
+      <c r="AB110" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC110" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="111" spans="1:30">
       <c r="A111">
         <v>2926358</v>
       </c>
@@ -9476,37 +9494,37 @@
         <v>2024</v>
       </c>
       <c r="H111" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="I111" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="J111" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="K111" t="s">
-        <v>770</v>
-      </c>
-      <c r="W111" t="s">
-        <v>32</v>
-      </c>
-      <c r="X111" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="Y111" t="s">
-        <v>772</v>
+        <v>34</v>
       </c>
       <c r="Z111" t="s">
-        <v>35</v>
+        <v>774</v>
       </c>
       <c r="AA111" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="AB111" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="112" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC111" t="s">
+        <v>776</v>
+      </c>
+      <c r="AD111" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="112" spans="1:30">
       <c r="A112">
         <v>2928146</v>
       </c>
@@ -9529,16 +9547,16 @@
         <v>2024</v>
       </c>
       <c r="H112" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="I112" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="J112" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="K112" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="P112">
         <v>0</v>
@@ -9546,26 +9564,26 @@
       <c r="T112">
         <v>0</v>
       </c>
-      <c r="W112" t="s">
-        <v>32</v>
-      </c>
-      <c r="X112" t="s">
-        <v>778</v>
-      </c>
       <c r="Y112" t="s">
-        <v>779</v>
+        <v>34</v>
       </c>
       <c r="Z112" t="s">
-        <v>35</v>
+        <v>781</v>
       </c>
       <c r="AA112" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="AB112" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="113" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC112" t="s">
+        <v>783</v>
+      </c>
+      <c r="AD112" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="113" spans="1:30">
       <c r="A113">
         <v>2930282</v>
       </c>
@@ -9588,16 +9606,16 @@
         <v>2024</v>
       </c>
       <c r="H113" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="I113" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="J113" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="K113" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="P113">
         <v>0</v>
@@ -9605,26 +9623,26 @@
       <c r="T113">
         <v>0</v>
       </c>
-      <c r="W113" t="s">
-        <v>32</v>
-      </c>
-      <c r="X113" t="s">
-        <v>785</v>
-      </c>
       <c r="Y113" t="s">
-        <v>786</v>
+        <v>34</v>
       </c>
       <c r="Z113" t="s">
-        <v>35</v>
+        <v>788</v>
       </c>
       <c r="AA113" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="AB113" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="114" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC113" t="s">
+        <v>790</v>
+      </c>
+      <c r="AD113" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="114" spans="1:30">
       <c r="A114">
         <v>2931666</v>
       </c>
@@ -9647,16 +9665,16 @@
         <v>2024</v>
       </c>
       <c r="H114" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="I114" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="J114" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="K114" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="P114">
         <v>0</v>
@@ -9664,26 +9682,26 @@
       <c r="T114">
         <v>0</v>
       </c>
-      <c r="W114" t="s">
-        <v>32</v>
-      </c>
-      <c r="X114" t="s">
-        <v>791</v>
-      </c>
       <c r="Y114" t="s">
-        <v>792</v>
+        <v>34</v>
       </c>
       <c r="Z114" t="s">
-        <v>35</v>
+        <v>794</v>
       </c>
       <c r="AA114" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="AB114" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="115" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC114" t="s">
+        <v>796</v>
+      </c>
+      <c r="AD114" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="115" spans="1:30">
       <c r="A115">
         <v>2933128</v>
       </c>
@@ -9706,16 +9724,16 @@
         <v>2024</v>
       </c>
       <c r="H115" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="I115" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="J115" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="K115" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="P115">
         <v>0</v>
@@ -9723,26 +9741,26 @@
       <c r="T115">
         <v>0</v>
       </c>
-      <c r="W115" t="s">
-        <v>32</v>
-      </c>
-      <c r="X115" t="s">
-        <v>798</v>
-      </c>
       <c r="Y115" t="s">
-        <v>799</v>
+        <v>34</v>
       </c>
       <c r="Z115" t="s">
-        <v>35</v>
+        <v>801</v>
       </c>
       <c r="AA115" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="AB115" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="116" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC115" t="s">
+        <v>803</v>
+      </c>
+      <c r="AD115" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="116" spans="1:30">
       <c r="A116">
         <v>2934470</v>
       </c>
@@ -9765,16 +9783,16 @@
         <v>2024</v>
       </c>
       <c r="H116" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="I116" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="J116" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="K116" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="P116">
         <v>0</v>
@@ -9782,26 +9800,26 @@
       <c r="T116">
         <v>0</v>
       </c>
-      <c r="W116" t="s">
-        <v>32</v>
-      </c>
-      <c r="X116" t="s">
-        <v>805</v>
-      </c>
       <c r="Y116" t="s">
-        <v>806</v>
+        <v>34</v>
       </c>
       <c r="Z116" t="s">
-        <v>35</v>
+        <v>808</v>
       </c>
       <c r="AA116" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="AB116" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="117" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC116" t="s">
+        <v>810</v>
+      </c>
+      <c r="AD116" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="117" spans="1:30">
       <c r="A117">
         <v>2936060</v>
       </c>
@@ -9824,16 +9842,16 @@
         <v>2024</v>
       </c>
       <c r="H117" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="I117" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="J117" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="K117" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="P117">
         <v>0</v>
@@ -9841,26 +9859,26 @@
       <c r="T117">
         <v>0</v>
       </c>
-      <c r="W117" t="s">
-        <v>32</v>
-      </c>
-      <c r="X117" t="s">
-        <v>812</v>
-      </c>
       <c r="Y117" t="s">
-        <v>813</v>
+        <v>34</v>
       </c>
       <c r="Z117" t="s">
-        <v>35</v>
+        <v>815</v>
       </c>
       <c r="AA117" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="AB117" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="118" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC117" t="s">
+        <v>817</v>
+      </c>
+      <c r="AD117" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="118" spans="1:30">
       <c r="A118">
         <v>2937709</v>
       </c>
@@ -9883,16 +9901,16 @@
         <v>2024</v>
       </c>
       <c r="H118" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="I118" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="J118" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="K118" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="P118">
         <v>0</v>
@@ -9900,26 +9918,26 @@
       <c r="T118">
         <v>0</v>
       </c>
-      <c r="W118" t="s">
-        <v>32</v>
-      </c>
-      <c r="X118" t="s">
-        <v>819</v>
-      </c>
       <c r="Y118" t="s">
-        <v>820</v>
+        <v>34</v>
       </c>
       <c r="Z118" t="s">
-        <v>35</v>
+        <v>822</v>
       </c>
       <c r="AA118" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="AB118" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="119" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC118" t="s">
+        <v>824</v>
+      </c>
+      <c r="AD118" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="119" spans="1:30">
       <c r="A119">
         <v>2939116</v>
       </c>
@@ -9942,16 +9960,16 @@
         <v>2024</v>
       </c>
       <c r="H119" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="I119" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="J119" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="K119" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="P119">
         <v>0</v>
@@ -9959,32 +9977,32 @@
       <c r="T119">
         <v>0</v>
       </c>
-      <c r="U119">
+      <c r="W119">
         <v>5</v>
       </c>
-      <c r="V119">
+      <c r="X119">
         <v>5</v>
       </c>
-      <c r="W119" t="s">
-        <v>32</v>
-      </c>
-      <c r="X119" t="s">
-        <v>826</v>
-      </c>
       <c r="Y119" t="s">
-        <v>827</v>
+        <v>34</v>
       </c>
       <c r="Z119" t="s">
-        <v>35</v>
+        <v>829</v>
       </c>
       <c r="AA119" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="AB119" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="120" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC119" t="s">
+        <v>831</v>
+      </c>
+      <c r="AD119" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="120" spans="1:30">
       <c r="A120">
         <v>2940384</v>
       </c>
@@ -10007,16 +10025,16 @@
         <v>2024</v>
       </c>
       <c r="H120" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="I120" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="J120" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="K120" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="P120">
         <v>0</v>
@@ -10024,26 +10042,26 @@
       <c r="T120">
         <v>0</v>
       </c>
-      <c r="W120" t="s">
-        <v>32</v>
-      </c>
-      <c r="X120" t="s">
-        <v>833</v>
-      </c>
       <c r="Y120" t="s">
-        <v>834</v>
+        <v>34</v>
       </c>
       <c r="Z120" t="s">
-        <v>35</v>
+        <v>836</v>
       </c>
       <c r="AA120" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="AB120" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="121" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC120" t="s">
+        <v>838</v>
+      </c>
+      <c r="AD120" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="121" spans="1:30">
       <c r="A121">
         <v>2942226</v>
       </c>
@@ -10066,16 +10084,16 @@
         <v>2024</v>
       </c>
       <c r="H121" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="I121" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="J121" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="K121" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="P121">
         <v>0</v>
@@ -10083,26 +10101,26 @@
       <c r="T121">
         <v>0</v>
       </c>
-      <c r="W121" t="s">
-        <v>32</v>
-      </c>
-      <c r="X121" t="s">
-        <v>840</v>
-      </c>
       <c r="Y121" t="s">
-        <v>841</v>
+        <v>34</v>
       </c>
       <c r="Z121" t="s">
-        <v>35</v>
+        <v>843</v>
       </c>
       <c r="AA121" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="AB121" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="122" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC121" t="s">
+        <v>845</v>
+      </c>
+      <c r="AD121" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="122" spans="1:30">
       <c r="A122">
         <v>2943664</v>
       </c>
@@ -10125,13 +10143,13 @@
         <v>2024</v>
       </c>
       <c r="H122" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="I122" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="J122" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="P122">
         <v>0</v>
@@ -10139,20 +10157,20 @@
       <c r="T122">
         <v>0</v>
       </c>
-      <c r="W122" t="s">
-        <v>32</v>
-      </c>
       <c r="Y122" t="s">
-        <v>846</v>
-      </c>
-      <c r="Z122" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA122" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="123" spans="1:28">
+        <v>849</v>
+      </c>
+      <c r="AB122" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC122" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="123" spans="1:30">
       <c r="A123">
         <v>2945068</v>
       </c>
@@ -10175,16 +10193,16 @@
         <v>2024</v>
       </c>
       <c r="H123" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="I123" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="J123" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="K123" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="P123">
         <v>0</v>
@@ -10192,26 +10210,26 @@
       <c r="T123">
         <v>0</v>
       </c>
-      <c r="W123" t="s">
-        <v>32</v>
-      </c>
-      <c r="X123" t="s">
-        <v>851</v>
-      </c>
       <c r="Y123" t="s">
-        <v>852</v>
+        <v>34</v>
       </c>
       <c r="Z123" t="s">
-        <v>35</v>
+        <v>854</v>
       </c>
       <c r="AA123" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="AB123" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="124" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC123" t="s">
+        <v>856</v>
+      </c>
+      <c r="AD123" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="124" spans="1:30">
       <c r="A124">
         <v>2946606</v>
       </c>
@@ -10234,16 +10252,16 @@
         <v>2024</v>
       </c>
       <c r="H124" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="I124" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="J124" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="K124" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="P124">
         <v>0</v>
@@ -10251,26 +10269,26 @@
       <c r="T124">
         <v>0</v>
       </c>
-      <c r="W124" t="s">
-        <v>32</v>
-      </c>
-      <c r="X124" t="s">
-        <v>858</v>
-      </c>
       <c r="Y124" t="s">
-        <v>859</v>
+        <v>34</v>
       </c>
       <c r="Z124" t="s">
-        <v>35</v>
+        <v>861</v>
       </c>
       <c r="AA124" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="AB124" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="125" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC124" t="s">
+        <v>863</v>
+      </c>
+      <c r="AD124" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="125" spans="1:30">
       <c r="A125">
         <v>2947755</v>
       </c>
@@ -10293,13 +10311,13 @@
         <v>2024</v>
       </c>
       <c r="H125" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="I125" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="J125" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="P125">
         <v>0</v>
@@ -10307,20 +10325,20 @@
       <c r="T125">
         <v>0</v>
       </c>
-      <c r="W125" t="s">
-        <v>32</v>
-      </c>
       <c r="Y125" t="s">
-        <v>864</v>
-      </c>
-      <c r="Z125" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA125" t="s">
-        <v>864</v>
-      </c>
-    </row>
-    <row r="126" spans="1:28">
+        <v>867</v>
+      </c>
+      <c r="AB125" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC125" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="126" spans="1:30">
       <c r="A126">
         <v>2948901</v>
       </c>
@@ -10343,16 +10361,16 @@
         <v>2024</v>
       </c>
       <c r="H126" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="I126" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="J126" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="K126" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="P126">
         <v>0</v>
@@ -10360,32 +10378,32 @@
       <c r="T126">
         <v>0</v>
       </c>
-      <c r="U126">
+      <c r="W126">
         <v>11</v>
       </c>
-      <c r="V126">
+      <c r="X126">
         <v>11</v>
       </c>
-      <c r="W126" t="s">
-        <v>32</v>
-      </c>
-      <c r="X126" t="s">
-        <v>869</v>
-      </c>
       <c r="Y126" t="s">
-        <v>870</v>
+        <v>34</v>
       </c>
       <c r="Z126" t="s">
-        <v>35</v>
+        <v>872</v>
       </c>
       <c r="AA126" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="AB126" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="127" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC126" t="s">
+        <v>874</v>
+      </c>
+      <c r="AD126" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="127" spans="1:30">
       <c r="A127">
         <v>2949906</v>
       </c>
@@ -10408,16 +10426,16 @@
         <v>2024</v>
       </c>
       <c r="H127" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="I127" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="J127" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="K127" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="P127">
         <v>0</v>
@@ -10425,26 +10443,26 @@
       <c r="T127">
         <v>0</v>
       </c>
-      <c r="W127" t="s">
-        <v>32</v>
-      </c>
-      <c r="X127" t="s">
-        <v>876</v>
-      </c>
       <c r="Y127" t="s">
-        <v>877</v>
+        <v>34</v>
       </c>
       <c r="Z127" t="s">
-        <v>35</v>
+        <v>879</v>
       </c>
       <c r="AA127" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="AB127" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="128" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC127" t="s">
+        <v>881</v>
+      </c>
+      <c r="AD127" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="128" spans="1:30">
       <c r="A128">
         <v>2956574</v>
       </c>
@@ -10467,13 +10485,13 @@
         <v>2024</v>
       </c>
       <c r="H128" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="I128" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="J128" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="P128">
         <v>0</v>
@@ -10481,20 +10499,20 @@
       <c r="T128">
         <v>0</v>
       </c>
-      <c r="W128" t="s">
-        <v>32</v>
-      </c>
       <c r="Y128" t="s">
-        <v>882</v>
-      </c>
-      <c r="Z128" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA128" t="s">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="129" spans="1:28">
+        <v>885</v>
+      </c>
+      <c r="AB128" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC128" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="129" spans="1:30">
       <c r="A129">
         <v>2959237</v>
       </c>
@@ -10517,34 +10535,34 @@
         <v>2024</v>
       </c>
       <c r="H129" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="I129" t="s">
+        <v>887</v>
+      </c>
+      <c r="J129" t="s">
         <v>884</v>
       </c>
-      <c r="J129" t="s">
-        <v>881</v>
-      </c>
       <c r="P129">
         <v>0</v>
       </c>
       <c r="T129">
         <v>0</v>
       </c>
-      <c r="W129" t="s">
-        <v>32</v>
-      </c>
       <c r="Y129" t="s">
-        <v>885</v>
-      </c>
-      <c r="Z129" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA129" t="s">
-        <v>885</v>
-      </c>
-    </row>
-    <row r="130" spans="1:28">
+        <v>888</v>
+      </c>
+      <c r="AB129" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC129" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="130" spans="1:30">
       <c r="A130">
         <v>2961010</v>
       </c>
@@ -10567,37 +10585,37 @@
         <v>2024</v>
       </c>
       <c r="H130" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="I130" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="J130" t="s">
-        <v>888</v>
-      </c>
-      <c r="U130">
+        <v>891</v>
+      </c>
+      <c r="W130">
         <v>1</v>
       </c>
-      <c r="V130">
+      <c r="X130">
         <v>1</v>
       </c>
-      <c r="W130" t="s">
-        <v>32</v>
-      </c>
       <c r="Y130" t="s">
-        <v>889</v>
-      </c>
-      <c r="Z130" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA130" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="AB130" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="131" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC130" t="s">
+        <v>893</v>
+      </c>
+      <c r="AD130" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="131" spans="1:30">
       <c r="A131">
         <v>2961011</v>
       </c>
@@ -10620,37 +10638,37 @@
         <v>2024</v>
       </c>
       <c r="H131" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="I131" t="s">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="J131" t="s">
-        <v>893</v>
-      </c>
-      <c r="U131">
+        <v>896</v>
+      </c>
+      <c r="W131">
         <v>1</v>
       </c>
-      <c r="V131">
+      <c r="X131">
         <v>1</v>
       </c>
-      <c r="W131" t="s">
-        <v>32</v>
-      </c>
       <c r="Y131" t="s">
-        <v>894</v>
-      </c>
-      <c r="Z131" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA131" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="AB131" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="132" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC131" t="s">
+        <v>898</v>
+      </c>
+      <c r="AD131" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="132" spans="1:30">
       <c r="A132">
         <v>2962558</v>
       </c>
@@ -10673,13 +10691,13 @@
         <v>2024</v>
       </c>
       <c r="H132" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="I132" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="J132" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="P132">
         <v>0</v>
@@ -10687,17 +10705,17 @@
       <c r="T132">
         <v>0</v>
       </c>
-      <c r="W132" t="s">
-        <v>32</v>
-      </c>
       <c r="Y132" t="s">
-        <v>898</v>
-      </c>
-      <c r="Z132" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA132" t="s">
-        <v>898</v>
+        <v>901</v>
+      </c>
+      <c r="AB132" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC132" t="s">
+        <v>901</v>
       </c>
     </row>
   </sheetData>
